--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>docs/test-cases.md · docs/test-run-log.md · docs/test-plan.md</t>
+          <t>docs/qa/test-cases.md · docs/qa/test-run-log.md · docs/qa/test-plan.md · docs/qa/test-steps-draft.md</t>
         </is>
       </c>
     </row>
@@ -776,6 +776,13 @@
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>테스트 스텝은 2026-09-28 초안이다 — 2회전에서 수행하며 확정한다</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1237,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="40.5" customHeight="1">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
@@ -1250,7 +1257,13 @@
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr"/>
-      <c r="F2" s="11" t="inlineStr"/>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>1. ← 를 2초 누른다
+2. → 를 2초 누른다
+3. 이동 방향과 스프라이트가 바라보는 쪽을 본다</t>
+        </is>
+      </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
           <t>입력 방향으로 이동하고 스프라이트가 뒤집힌다</t>
@@ -1271,7 +1284,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="40.5" customHeight="1">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
@@ -1291,7 +1304,13 @@
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr"/>
-      <c r="F3" s="11" t="inlineStr"/>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>1. Space 를 아주 짧게 눌러 떼고 점프 높이를 본다
+2. 같은 자리에서 Space 를 끝까지 누른 채 점프한다
+3. 두 높이를 비교한다</t>
+        </is>
+      </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
           <t>버튼을 짧게 떼면 낮게, 끝까지 누르면 높게 뛴다</t>
@@ -1312,7 +1331,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="40.5" customHeight="1">
       <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
@@ -1332,7 +1351,13 @@
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr"/>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>1. 발판 끝까지 걸어간다
+2. 발판을 벗어난 직후(0.1초 안에) Space 를 누른다
+3. 점프가 나가는지 본다</t>
+        </is>
+      </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
           <t>발판을 떠난 직후에 눌러도 점프가 나간다</t>
@@ -1353,7 +1378,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
@@ -1373,7 +1398,13 @@
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr"/>
-      <c r="F5" s="11" t="inlineStr"/>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>1. 높은 곳에서 아래로 떨어진다
+2. 착지하기 직전(공중에서) Space 를 누른다
+3. 착지와 함께 점프가 나가는지 본다</t>
+        </is>
+      </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
           <t>착지 직전에 눌러도 점프가 씹히지 않는다</t>
@@ -1394,7 +1425,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="40.5" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
@@ -1414,7 +1445,13 @@
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>1. 방 안의 구멍(낙하 지점)을 찾아 그 위에 선다
+2. 구멍으로 떨어진다
+3. 복귀한 위치가 떨어지기 전 마지막으로 발을 붙였던 지점인지 본다</t>
+        </is>
+      </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
           <t>구멍에 떨어지면 마지막 접지 지점으로 돌아온다</t>
@@ -1435,7 +1472,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
@@ -1455,7 +1492,14 @@
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr"/>
-      <c r="F7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>1. 적 앞에서 F 를 누른다
+2. 1타 모션이 끝나기 전에 F 를 다시 누른다
+3. 같은 방식으로 3타까지 이어 누른다
+4. 세 타가 끊기지 않고 이어지는지 본다</t>
+        </is>
+      </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
           <t>연속 입력이 다음 타로 이어진다</t>
@@ -1476,7 +1520,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>7</v>
       </c>
@@ -1496,7 +1540,14 @@
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>1. F 로 1타를 낸다
+2. 아무 입력 없이 2초 기다린다
+3. 다시 F 를 누른다
+4. 나가는 모션이 2타인지 1타인지 본다</t>
+        </is>
+      </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
           <t>입력이 끊기면 1타부터 다시 시작한다</t>
@@ -1517,7 +1568,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="40.5" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
@@ -1537,7 +1588,13 @@
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr"/>
-      <c r="F9" s="11" t="inlineStr"/>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>1. 적에게 F 로 한 대 맞힌다
+2. 타격이 닿는 순간 화면을 본다
+3. 셋이 동시에 나는지 각각 확인한다 — 동작이 멈추는가 · 적이 밀리는가 · 화면이 흔들리는가</t>
+        </is>
+      </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
           <t>타격 순간 셋이 함께 난다</t>
@@ -1558,7 +1615,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
@@ -1578,7 +1635,13 @@
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>1. 적 공격에 일부러 한 번 맞는다
+2. 맞은 직후 적 앞에 그대로 서 있는다
+3. 스프라이트가 깜빡이는 동안 HUD 체력이 더 줄어드는지 본다</t>
+        </is>
+      </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
           <t>맞으면 깜빡이고 그동안 다시 안 맞는다</t>
@@ -1599,7 +1662,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>10</v>
       </c>
@@ -1619,7 +1682,14 @@
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr"/>
-      <c r="F11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>1. 적 2마리가 함께 있는 방에서 둘 사이로 들어간다
+2. 한쪽 공격에 맞는다
+3. 깜빡이는 동안 다른 쪽 공격에 몸을 댄다
+4. 두 번째 피해가 들어가는지 본다</t>
+        </is>
+      </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
           <t>무적 중에 두 번째 적에게 이어서 안 갈린다</t>
@@ -1640,7 +1710,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="40.5" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>11</v>
       </c>
@@ -1660,7 +1730,13 @@
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr"/>
-      <c r="F12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>1. 지상에서 적과 조금 떨어져 선다
+2. 발 위치를 기억하고 F 를 누른다
+3. 공격이 끝난 뒤 발 위치가 앞으로 옮겨졌는지 본다</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
           <t>공격하면서 조금 앞으로 나간다</t>
@@ -1681,7 +1757,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="40.5" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>12</v>
       </c>
@@ -1701,7 +1777,13 @@
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr"/>
-      <c r="F13" s="11" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>1. HUD 체력 구슬의 현재 상태를 본다
+2. 적 공격에 한 번 맞는다
+3. HUD 체력이 줄어드는지 본다</t>
+        </is>
+      </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
           <t>맞으면 HUD 체력이 줄어든다</t>
@@ -1722,7 +1804,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="54" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>13</v>
       </c>
@@ -1742,7 +1824,14 @@
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr"/>
-      <c r="F14" s="11" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>1. Space 로 점프한다
+2. 공중에서 F 로 공격한다
+3. 공격 모션이 끝나기 전에 착지한다
+4. 착지 직후 ← → 입력으로 이동이 되는지 본다</t>
+        </is>
+      </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
           <t>착지 후에는 공격 중 이동이 막힌다</t>
@@ -1767,7 +1856,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="40.5" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>14</v>
       </c>
@@ -1787,7 +1876,13 @@
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>1. 현재 플레이어 외형과 HUD 슬롯 표시를 본다
+2. A 로 무기를 바꾼다
+3. 외형이 바뀐 뒤 F 로 공격해 모션도 바뀌었는지 본다</t>
+        </is>
+      </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
           <t>스프라이트·애니메이션이 동시에 교체된다</t>
@@ -1808,7 +1903,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="40.5" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>15</v>
       </c>
@@ -1828,7 +1923,13 @@
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>1. 적 공격 예고가 뜨는 것을 보고 그 앞에 선다
+2. 공격이 닿는 타이밍에 A 를 누른다
+3. HUD 체력이 줄어드는지 본다</t>
+        </is>
+      </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
           <t>대시 중 적 공격에 체력이 안 깎인다</t>
@@ -1849,7 +1950,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="40.5" customHeight="1">
       <c r="A17" s="11" t="n">
         <v>16</v>
       </c>
@@ -1869,7 +1970,13 @@
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr"/>
-      <c r="F17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>1. A 로 무기를 바꾼다
+2. 스왑 게이지가 차기 전에 A 를 다시 누른다
+3. 무기가 바뀌는지 · 게이지가 초기화되는지 본다</t>
+        </is>
+      </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
           <t>게이지가 안 찼으면 입력이 무시된다</t>
@@ -1890,7 +1997,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="40.5" customHeight="1">
       <c r="A18" s="11" t="n">
         <v>17</v>
       </c>
@@ -1910,7 +2017,13 @@
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>1. A 로 무기를 바꾼다
+2. 교체 순간을 영상으로 녹화하거나 연속 캡처한다
+3. 프레임을 넘겨 보며 옛 무기 그림이 한 프레임이라도 남는지 본다</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
           <t>교체 순간 옛 무기 그림이 한 프레임도 안 보인다</t>
@@ -1931,7 +2044,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="40.5" customHeight="1">
       <c r="A19" s="11" t="n">
         <v>18</v>
       </c>
@@ -1951,7 +2064,13 @@
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>1. HUD 무기 슬롯 두 칸의 글자를 읽는다
+2. A 로 바꾼 뒤 다시 읽는다
+3. `검` 처럼 읽히는지, `weapon.sword.name` 같은 키가 보이는지 본다</t>
+        </is>
+      </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
           <t>로컬라이즈 키가 아니라 검 처럼 읽힌다</t>
@@ -1972,7 +2091,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="40.5" customHeight="1">
       <c r="A20" s="11" t="n">
         <v>19</v>
       </c>
@@ -1992,7 +2111,13 @@
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>1. A 를 눌러 대시를 시작한다
+2. 대시가 끝나기 전에 ← → · Space · F · A 를 차례로 누른다
+3. 넷 중 하나라도 반응하는지 본다</t>
+        </is>
+      </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
           <t>대시 중 이동·점프·공격·재스왑이 전부 안 먹는다</t>
@@ -2013,7 +2138,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="11" t="n">
         <v>20</v>
       </c>
@@ -2033,7 +2158,14 @@
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr"/>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>1. 검으로 적을 때려 닿는 거리와 타격 간격을 본다
+2. 창으로 바꿔 같은 거리에서 때려 본다
+3. 활로 바꿔 같은 거리에서 쏴 본다
+4. 셋의 사거리와 리듬이 구분되는지 본다</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
           <t>검·창·활의 사거리와 리듬이 구분된다</t>
@@ -2054,7 +2186,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="40.5" customHeight="1">
       <c r="A22" s="11" t="n">
         <v>21</v>
       </c>
@@ -2074,7 +2206,13 @@
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr"/>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>1. 적을 향해 F 로 화살을 쏜다
+2. 명중한 뒤 화살이 화면에 남는지 본다
+3. 플레이어 쪽으로도 쏴서 자기 피해가 들어가는지 본다</t>
+        </is>
+      </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
           <t>명중하면 소멸하고 발사자는 안 때린다</t>
@@ -2095,7 +2233,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="40.5" customHeight="1">
       <c r="A23" s="11" t="n">
         <v>22</v>
       </c>
@@ -2115,7 +2253,13 @@
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr"/>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>1. 적이 없는 방향으로 F 를 3분 이상 연타한다
+2. 프레임을 관찰한다
+3. 에디터면 Hierarchy 에서 화살 오브젝트 수가 계속 늘어나는지 본다</t>
+        </is>
+      </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
           <t>몇 분 돌려도 프레임이 안 떨어진다</t>
@@ -2136,7 +2280,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="40.5" customHeight="1">
       <c r="A24" s="11" t="n">
         <v>23</v>
       </c>
@@ -2156,7 +2300,13 @@
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr"/>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>1. 빌드를 실행해 새 런을 시작한다
+2. 보상방에서 무기 카드를 받아 세 무기를 순서대로 모은다
+3. 검 · 창 · 활 셋을 런 안에서 전부 손에 쥘 수 있는지 본다</t>
+        </is>
+      </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
           <t>세 무기를 런 안에서 전부 쓸 수 있다</t>
@@ -2177,7 +2327,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="54" customHeight="1">
       <c r="A25" s="11" t="n">
         <v>24</v>
       </c>
@@ -2197,7 +2347,14 @@
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr"/>
-      <c r="F25" s="11" t="inlineStr"/>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>1. Unity 에디터에서 Window &gt; General &gt; Test Runner 를 연다
+2. EditMode 탭의 WeaponInstanceTests 를 펼친다
+3. 강화_1레벨에_데미지가_최소_1은_오른다 · 원본이_크면_배율이_가드를_이긴다 ·
+강화하면_선딜과_후딜이_줄어든다 · 강화해도_activeTime_은_안_변한다 넷을 실행한다</t>
+        </is>
+      </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
           <t>강화 후 같은 적을 더 적은 타수로 잡는다</t>
@@ -2222,7 +2379,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="11" t="n">
         <v>25</v>
       </c>
@@ -2242,7 +2399,12 @@
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr"/>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>1. Test Runner 의 EditMode 탭에서 WeaponInstanceTests 를 펼친다
+2. GetAttack_은_원본_SO_를_바꾸지_않는다 · 강화_0레벨이면_원본_그대로다 둘을 실행한다</t>
+        </is>
+      </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
           <t>플레이 모드를 넘어 WeaponData 가 그대로다</t>
@@ -2267,7 +2429,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="11" t="n">
         <v>26</v>
       </c>
@@ -2287,7 +2449,12 @@
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr"/>
-      <c r="F27" s="11" t="inlineStr"/>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>1. Test Runner 의 EditMode 탭에서 WeaponInstanceTests 를 펼친다
+2. 생성자에_음수_레벨을_주면_0_이_된다 · Upgrade_는_0_이하를_무시한다 둘을 실행한다</t>
+        </is>
+      </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
           <t>레벨당 최소 +1 · 음수 레벨은 0 으로</t>
@@ -2312,7 +2479,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="40.5" customHeight="1">
       <c r="A28" s="11" t="n">
         <v>27</v>
       </c>
@@ -2332,7 +2499,13 @@
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr"/>
-      <c r="F28" s="11" t="inlineStr"/>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>1. 적의 시야 밖에서 천천히 다가간다
+2. 적이 따라오기 시작하는 지점을 본다
+3. 예고 색이 뜨고, 공격이 나가고, 공격 뒤 적이 멈추는 것까지 순서대로 본다</t>
+        </is>
+      </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
           <t>네 단계가 순서대로 보인다</t>
@@ -2353,7 +2526,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="40.5" customHeight="1">
       <c r="A29" s="11" t="n">
         <v>28</v>
       </c>
@@ -2373,7 +2546,13 @@
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr"/>
-      <c r="F29" s="11" t="inlineStr"/>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>1. 적에게 다가가 공격 예고가 뜨게 한다
+2. 예고 순간 적 스프라이트 색을 본다
+3. 색이 바뀐 것을 화면에서 알 수 있는지 판정한다</t>
+        </is>
+      </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
           <t>공격 직전 색 변화가 화면에 나온다</t>
@@ -2394,7 +2573,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="40.5" customHeight="1">
       <c r="A30" s="11" t="n">
         <v>29</v>
       </c>
@@ -2414,7 +2593,13 @@
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr"/>
-      <c r="F30" s="11" t="inlineStr"/>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>1. 적에게 다가가 예고가 뜨게 한다
+2. 예고 중에 F 로 때린다
+3. 예고와 공격이 중단되는지 본다</t>
+        </is>
+      </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
           <t>때리면 예고·공격이 중단된다 (#79)</t>
@@ -2435,7 +2620,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="40.5" customHeight="1">
       <c r="A31" s="11" t="n">
         <v>30</v>
       </c>
@@ -2455,7 +2640,13 @@
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr"/>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>1. 적이 공격 모션을 시작하게 만든다
+2. 공격이 닿기 전에 마지막 타로 적을 처치한다
+3. 시체가 사라지는 동안 몸을 겹쳐 두고 체력이 줄어드는지 본다</t>
+        </is>
+      </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
           <t>죽은 적의 공격 판정이 남지 않는다 (#55)</t>
@@ -2476,7 +2667,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="54" customHeight="1">
       <c r="A32" s="11" t="n">
         <v>31</v>
       </c>
@@ -2496,7 +2687,14 @@
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr"/>
-      <c r="F32" s="11" t="inlineStr"/>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>1. 적에게 몸이 닿을 만큼 붙어 공격을 받는다
+2. 어떤 패턴이 나오는지 적는다
+3. 화면 반 폭쯤 떨어져 다시 공격을 받는다
+4. 두 거리에서 나온 패턴이 다른지 본다</t>
+        </is>
+      </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
           <t>붙으면 물기, 떨어지면 돌진이 나온다</t>
@@ -2517,7 +2715,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="40.5" customHeight="1">
       <c r="A33" s="11" t="n">
         <v>32</v>
       </c>
@@ -2537,7 +2735,13 @@
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr"/>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>1. 방에 들어간 직후, 적에게 다가가기 전에 화면을 본다
+2. 두 적의 외형만 보고 어느 쪽이 원거리형인지 지목한다
+3. 다가가서 실제 행동으로 맞는지 확인한다</t>
+        </is>
+      </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
           <t>붙기 전에 돌진형·원거리형을 구분할 수 있다</t>
@@ -2562,7 +2766,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="40.5" customHeight="1">
       <c r="A34" s="11" t="n">
         <v>33</v>
       </c>
@@ -2582,7 +2786,13 @@
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr"/>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>1. 원거리형 적에게 정면으로 걸어간다
+2. 사거리 안으로 들어갈 때 적의 발 위치를 본다
+3. 적이 뒤로 물러나는지 본다</t>
+        </is>
+      </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
           <t>플레이어가 붙으면 거리를 벌린다 (#108)</t>
@@ -2603,7 +2813,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="54" customHeight="1">
       <c r="A35" s="11" t="n">
         <v>34</v>
       </c>
@@ -2623,7 +2833,14 @@
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr"/>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>1. 보스와 몸이 닿는 거리에서 버틴다 — Smash(0~1.8)
+2. 조금 물러나 중거리를 유지한다 — Charge(1.6~3.5)
+3. 화면 폭만큼 멀리 떨어진다 — Throw(3~10)
+4. 세 패턴을 한 보스전에서 모두 봤는지 적는다</t>
+        </is>
+      </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
           <t>한 보스전에서 셋을 다 본다</t>
@@ -2644,7 +2861,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="40.5" customHeight="1">
       <c r="A36" s="11" t="n">
         <v>35</v>
       </c>
@@ -2664,7 +2881,13 @@
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr"/>
-      <c r="F36" s="11" t="inlineStr"/>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>1. 보스가 패턴을 시작하게 만든다
+2. 예고 중에 F 로 연타한다
+3. 보스 공격이 중단되는지 본다</t>
+        </is>
+      </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
           <t>때려도 보스 공격이 중단되지 않는다</t>
@@ -2685,7 +2908,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="40.5" customHeight="1">
       <c r="A37" s="11" t="n">
         <v>36</v>
       </c>
@@ -2705,7 +2928,13 @@
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr"/>
-      <c r="F37" s="11" t="inlineStr"/>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>1. Test Runner 의 EditMode 탭에서 AssetDataTests 를 펼친다
+2. 모든_패턴이_minRange_보다_maxRange_가_크다 · 보스_패턴이_0부터_10까지_구멍_없이_덮는다 ·
+근접_패턴_둘이_겹치고_가중치가_3대1_이다 · 근접은_높이_제한이_있고_원거리는_없다 넷을 실행한다</t>
+        </is>
+      </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
           <t>보스 010 · 근접에는 높이 제한이 있다</t>
@@ -2730,7 +2959,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="40.5" customHeight="1">
       <c r="A38" s="11" t="n">
         <v>37</v>
       </c>
@@ -2750,7 +2979,13 @@
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr"/>
-      <c r="F38" s="11" t="inlineStr"/>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>1. 보스가 패턴을 시작할 때까지 거리를 유지한다
+2. 예고 구간(0.4~0.8초)에 보스 스프라이트 색을 본다
+3. 색 변화를 화면에서 알 수 있는지 판정하고 그 순간을 캡처한다</t>
+        </is>
+      </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
           <t>공격 직전 보스 스프라이트 색이 변한다</t>
@@ -2783,7 +3018,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="40.5" customHeight="1">
       <c r="A39" s="11" t="n">
         <v>38</v>
       </c>
@@ -2803,7 +3038,13 @@
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr"/>
-      <c r="F39" s="11" t="inlineStr"/>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>1. 전투방의 적을 전부 처치한다
+2. 열린 출구 포탈까지 이동한다
+3. 포탈을 밟아 다음 방으로 넘어가는지 본다</t>
+        </is>
+      </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
           <t>출구 포탈로 다음 방에 들어간다</t>
@@ -2824,7 +3065,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="54" customHeight="1">
       <c r="A40" s="11" t="n">
         <v>39</v>
       </c>
@@ -2844,7 +3085,14 @@
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr"/>
-      <c r="F40" s="11" t="inlineStr"/>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>1. 전투방에 들어가 무엇이 일어나는지 적는다 — 적이 나오는가
+2. 보상방에 들어가 무엇이 일어나는지 적는다 — 카드가 뜨는가
+3. 보스방에 들어가 무엇이 일어나는지 적는다 — 보스가 나오는가
+4. 셋이 서로 다르게 동작하는지 본다</t>
+        </is>
+      </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
           <t>전투·보상·보스방이 각각 다르게 동작한다</t>
@@ -2865,7 +3113,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="40.5" customHeight="1">
       <c r="A41" s="11" t="n">
         <v>40</v>
       </c>
@@ -2885,7 +3133,13 @@
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr"/>
-      <c r="F41" s="11" t="inlineStr"/>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>1. 출구 포탈을 밟아 다음 방으로 넘어간다
+2. 전환 직후 화면을 본다
+3. 플레이어와 새 방이 화면 안에 잡히는지 본다</t>
+        </is>
+      </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
           <t>전환 후 새 방이 화면에 잡힌다</t>
@@ -2906,7 +3160,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="40.5" customHeight="1">
       <c r="A42" s="11" t="n">
         <v>41</v>
       </c>
@@ -2930,7 +3184,13 @@
           <t>시드 099</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr"/>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>1. Test Runner 의 EditMode 탭에서 RunStateTests 를 펼친다
+2. 한_런에_전투방이_겹치지_않는다 를 실행한다
+3. 시드 0~99 전부 통과하는지 본다 — 실패하면 메시지에 시드 번호가 찍힌다</t>
+        </is>
+      </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
           <t>전투방 5개가 서로 다르다</t>
@@ -2955,7 +3215,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="27" customHeight="1">
       <c r="A43" s="11" t="n">
         <v>42</v>
       </c>
@@ -2979,7 +3239,12 @@
           <t>같은 시드로 2회</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr"/>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>1. Test Runner 의 EditMode 탭에서 RunStateTests 를 펼친다
+2. 같은_시드는_같은_방_순서다 를 실행한다</t>
+        </is>
+      </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
           <t>방 순서가 동일하다</t>
@@ -3004,7 +3269,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="40.5" customHeight="1">
       <c r="A44" s="11" t="n">
         <v>43</v>
       </c>
@@ -3024,7 +3289,13 @@
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>1. 전투방에서 플레이어를 타일 바닥 옆에 세운다
+2. 캡처해서 타일 한 칸과 캐릭터의 픽셀 크기를 비교한다
+3. 같은 해상도(PPU 32)로 보이는지 본다</t>
+        </is>
+      </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
           <t>타일이 캐릭터와 같은 해상도로 보인다 (PPU 32)</t>
@@ -3045,7 +3316,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="40.5" customHeight="1">
       <c r="A45" s="11" t="n">
         <v>44</v>
       </c>
@@ -3069,7 +3340,13 @@
           <t>시드 099 · roomCount 7</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr"/>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>1. Test Runner 의 EditMode 탭에서 RunStateTests 를 펼친다
+2. 덱_경계에서_같은_방이_연속되지_않는다 를 실행한다
+3. roomCount 7 · 시드 0~99 에서 5번째와 6번째 방이 다른지 본다</t>
+        </is>
+      </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
           <t>5번째와 6번째 방이 다르다</t>
@@ -3094,7 +3371,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="27" customHeight="1">
       <c r="A46" s="11" t="n">
         <v>45</v>
       </c>
@@ -3118,7 +3395,12 @@
           <t>시드 099</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr"/>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>1. Test Runner 의 EditMode 탭에서 RunStateTests 를 펼친다
+2. 시드가_다르면_순서도_달라진다 를 실행한다</t>
+        </is>
+      </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
           <t>서로 다른 순서가 둘 이상 나온다</t>
@@ -3143,7 +3425,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="54" customHeight="1">
       <c r="A47" s="11" t="n">
         <v>46</v>
       </c>
@@ -3163,7 +3445,14 @@
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr"/>
-      <c r="F47" s="11" t="inlineStr"/>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>1. 새 런을 시작하고 Player.log 에 찍힌 시드를 적어 둔다
+2. 전투방 5칸과 보상방 4칸을 순서대로 지난다
+3. 보스방에서 보스를 처치한다
+4. 결과 화면까지 끊김 없이 도달했는지 본다</t>
+        </is>
+      </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
           <t>시작 → 전투 → 보상 → 보스 → 결과가 끊기지 않는다</t>
@@ -3184,7 +3473,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="40.5" customHeight="1">
       <c r="A48" s="11" t="n">
         <v>47</v>
       </c>
@@ -3204,7 +3493,13 @@
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr"/>
-      <c r="F48" s="11" t="inlineStr"/>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>1. 보스방에서 보스를 처치한다
+2. 결과 화면이 뜨는지 본다
+3. 결과 문구가 클리어인지 사망인지 읽는다</t>
+        </is>
+      </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
           <t>결과 화면이 클리어로 뜬다</t>
@@ -3225,7 +3520,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="40.5" customHeight="1">
       <c r="A49" s="11" t="n">
         <v>48</v>
       </c>
@@ -3245,7 +3540,13 @@
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr"/>
-      <c r="F49" s="11" t="inlineStr"/>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>1. 적 공격을 계속 맞아 체력을 0으로 만든다
+2. 결과 화면이 뜨는지 본다
+3. 결과 문구가 사망인지 읽는다</t>
+        </is>
+      </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
           <t>죽으면 결과 화면이 뜬다</t>
@@ -3266,7 +3567,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="40.5" customHeight="1">
       <c r="A50" s="11" t="n">
         <v>49</v>
       </c>
@@ -3286,7 +3587,13 @@
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr"/>
-      <c r="F50" s="11" t="inlineStr"/>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>1. 결과 화면에서 R 을 누른다
+2. 새 런이 시작되는지 본다
+3. Player.log 의 새 시드가 직전 런과 다른지 본다</t>
+        </is>
+      </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
           <t>새 시드로 처음부터 다시 시작한다</t>
@@ -3307,7 +3614,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="54" customHeight="1">
       <c r="A51" s="11" t="n">
         <v>50</v>
       </c>
@@ -3327,7 +3634,14 @@
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr"/>
-      <c r="F51" s="11" t="inlineStr"/>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>1. 결과 화면에 적힌 체력 · 무기 · 강화 · 킬 수를 적어 둔다
+2. R 로 재시작한다
+3. HUD 의 체력 · 무기 슬롯 · 강화 수치가 초기 상태인지 본다
+4. 첫 처치 전 킬 수가 0인지 본다</t>
+        </is>
+      </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
           <t>체력·무기·강화·킬 수가 전부 초기화된다</t>
@@ -3348,7 +3662,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="40.5" customHeight="1">
       <c r="A52" s="11" t="n">
         <v>51</v>
       </c>
@@ -3368,7 +3682,13 @@
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr"/>
-      <c r="F52" s="11" t="inlineStr"/>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>1. 보상방에 들어가 카드가 몇 장 뜨는지 본다
+2. 카드 셋의 내용을 읽는다 — 무기 · 회복 · 강화
+3. 하나를 골라 적용되는지 본다</t>
+        </is>
+      </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
           <t>무기·회복·강화 중 하나를 고른다</t>
@@ -3389,7 +3709,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="27" customHeight="1">
       <c r="A53" s="11" t="n">
         <v>52</v>
       </c>
@@ -3409,7 +3729,12 @@
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr"/>
-      <c r="F53" s="11" t="inlineStr"/>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>1. 보상방의 무기 카드에 적힌 무기 이름을 읽는다
+2. 지금 든 두 무기와 같은 것이 있는지 본다</t>
+        </is>
+      </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
           <t>이미 든 무기가 카드로 안 나온다</t>
@@ -3430,7 +3755,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="40.5" customHeight="1">
       <c r="A54" s="11" t="n">
         <v>53</v>
       </c>
@@ -3450,7 +3775,13 @@
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr"/>
-      <c r="F54" s="11" t="inlineStr"/>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>1. 보상방에 들어간다
+2. 전투방과 구분되는 표시가 화면에 있는지 본다
+3. 아무 표시 없이 지나칠 수 있는지 판정한다</t>
+        </is>
+      </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
           <t>들어간 것을 표시 없이 지나치지 않는다</t>
@@ -3475,7 +3806,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="40.5" customHeight="1">
       <c r="A55" s="11" t="n">
         <v>54</v>
       </c>
@@ -3495,7 +3826,13 @@
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr"/>
-      <c r="F55" s="11" t="inlineStr"/>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>1. HUD 체력을 보고 현재 값을 적어 둔다
+2. 적 1마리를 처치한다
+3. 체력이 오르는지 본다</t>
+        </is>
+      </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
           <t>적을 잡으면 체력이 조금 오른다</t>
@@ -3516,7 +3853,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="40.5" customHeight="1">
       <c r="A56" s="11" t="n">
         <v>55</v>
       </c>
@@ -3536,7 +3873,13 @@
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr"/>
-      <c r="F56" s="11" t="inlineStr"/>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>1. 숫자키 1 로 카드를 고른다
+2. 선택 패널이 사라지는지 본다
+3. 클릭으로 고르는 경우와 비교한다 — 같은 방을 다시 만들어 클릭으로 고른다</t>
+        </is>
+      </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
           <t>클릭이든 숫자키든 패널이 사라진다</t>
@@ -3569,7 +3912,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="40.5" customHeight="1">
       <c r="A57" s="11" t="n">
         <v>56</v>
       </c>
@@ -3589,7 +3932,13 @@
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr"/>
-      <c r="F57" s="11" t="inlineStr"/>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>1. 게임을 완전히 종료한다
+2. 실행 파일을 실행하고 시작 화면이 처음 뜨는 순간을 녹화한다
+3. 프레임을 넘겨 보며 글자가 한 프레임이라도 깜빡이는지 본다</t>
+        </is>
+      </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
           <t>켜자마자 글자가 깜빡이지 않는다</t>
@@ -3614,7 +3963,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="40.5" customHeight="1">
       <c r="A58" s="11" t="n">
         <v>57</v>
       </c>
@@ -3634,7 +3983,13 @@
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr"/>
-      <c r="F58" s="11" t="inlineStr"/>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>1. 시작 화면에서 게임 시작을 눌러 런이 시작되는지 본다
+2. 시작 화면으로 돌아와 도움말을 눌러 조작표가 뜨는지 본다
+3. 종료를 눌러 창이 닫히는지 본다</t>
+        </is>
+      </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
           <t>게임 시작 · 조작 안내 · 종료가 동작한다</t>
@@ -3655,7 +4010,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="40.5" customHeight="1">
       <c r="A59" s="11" t="n">
         <v>58</v>
       </c>
@@ -3675,7 +4030,13 @@
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr"/>
-      <c r="F59" s="11" t="inlineStr"/>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>1. 전투 중 ESC 를 누른다
+2. 게임이 멈추는지 본다
+3. 설정 패널이 열리는지 본다</t>
+        </is>
+      </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
           <t>전투 중 ESC 로 멈추고 설정이 열린다</t>
@@ -3696,7 +4057,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="54" customHeight="1">
       <c r="A60" s="11" t="n">
         <v>59</v>
       </c>
@@ -3716,7 +4077,14 @@
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr"/>
-      <c r="F60" s="11" t="inlineStr"/>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>1. 해상도를 다른 값으로 바꾸고 화면이 바뀌는지 본다
+2. 화면 모드를 바꾸고 창/전체화면이 바뀌는지 본다
+3. 전체 · 배경음 · 효과음 슬라이더를 각각 움직이고 소리가 바뀌는지 듣는다
+4. 언어를 English 로 바꾸고 글자가 바뀌는지 본다</t>
+        </is>
+      </c>
       <c r="G60" s="11" t="inlineStr">
         <is>
           <t>해상도·화면 모드·볼륨·언어가 즉시 반영된다</t>
@@ -3737,7 +4105,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="40.5" customHeight="1">
       <c r="A61" s="11" t="n">
         <v>60</v>
       </c>
@@ -3757,7 +4125,13 @@
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr"/>
-      <c r="F61" s="11" t="inlineStr"/>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>1. 설정에서 해상도 · 볼륨 · 언어를 기본값과 다르게 바꾼다
+2. 게임을 완전히 종료한다
+3. 다시 실행해 설정 화면을 열고 바꾼 값이 남아 있는지 본다</t>
+        </is>
+      </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
           <t>껐다 켜도 설정이 유지된다</t>
@@ -3778,7 +4152,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="40.5" customHeight="1">
       <c r="A62" s="11" t="n">
         <v>61</v>
       </c>
@@ -3798,7 +4172,13 @@
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr"/>
-      <c r="F62" s="11" t="inlineStr"/>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>1. 시작 화면의 설정을 열어 항목을 세어 둔다 — 언어가 있다
+2. 런을 시작하고 전투 중 ESC 로 설정을 연다
+3. 언어 항목이 있는지 본다</t>
+        </is>
+      </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
           <t>전투 씬 설정에는 언어가 안 보인다</t>
@@ -3819,7 +4199,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="40.5" customHeight="1">
       <c r="A63" s="11" t="n">
         <v>62</v>
       </c>
@@ -3839,7 +4219,13 @@
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr"/>
-      <c r="F63" s="11" t="inlineStr"/>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>1. 시작 화면에서 도움말을 연다
+2. 규칙 설명 문단을 본다
+3. 글자가 상자 밖으로 넘치거나 잘리는지 본다</t>
+        </is>
+      </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
           <t>영어로 바꿔도 글자가 상자를 안 넘는다</t>
@@ -3864,7 +4250,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="40.5" customHeight="1">
       <c r="A64" s="11" t="n">
         <v>63</v>
       </c>
@@ -3884,7 +4270,13 @@
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr"/>
-      <c r="F64" s="11" t="inlineStr"/>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>1. 적 공격에 맞고 체력 바가 줄어드는지 본다
+2. A 로 무기를 바꾸고 슬롯 표시가 따라오는지 본다
+3. 스왑 직후 게이지가 차오르는지 본다</t>
+        </is>
+      </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
           <t>체력 바·무기 슬롯·스왑 게이지가 상태를 따라간다</t>
@@ -3905,7 +4297,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="40.5" customHeight="1">
       <c r="A65" s="11" t="n">
         <v>64</v>
       </c>
@@ -3925,7 +4317,13 @@
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr"/>
-      <c r="F65" s="11" t="inlineStr"/>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>1. 영어 상태로 런을 시작한다
+2. 사망하거나 보스를 처치해 결과 화면을 띄운다
+3. 결과 · 요약 · 안내 · 버튼의 글자가 전부 영어인지 읽는다</t>
+        </is>
+      </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
           <t>영어에서 결과 화면이 한국어로 안 나온다</t>
@@ -3946,7 +4344,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="54" customHeight="1">
       <c r="A66" s="11" t="n">
         <v>65</v>
       </c>
@@ -3966,7 +4364,14 @@
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr"/>
-      <c r="F66" s="11" t="inlineStr"/>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>1. 레지스트리에서 이 게임의 저장 키를 지운다
+(HKCU\Software\&lt;companyName&gt;\WeaponHero)
+2. 게임을 실행하고 설정 화면을 연다
+3. 전체 1 · 배경음 0.8 · 효과음 1 인지 읽는다</t>
+        </is>
+      </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
           <t>저장된 설정이 없으면 master 1 · bgm 0.8 · sfx 1 로 시작한다</t>
@@ -3987,7 +4392,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="40.5" customHeight="1">
       <c r="A67" s="11" t="n">
         <v>66</v>
       </c>
@@ -4007,7 +4412,13 @@
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr"/>
-      <c r="F67" s="11" t="inlineStr"/>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>1. 도움말의 조작표와 규칙 설명에 적힌 조작을 전부 적어 둔다
+2. 런에서 그 조작을 하나씩 눌러 전부 동작하는지 본다
+3. 반대로 동작하는 조작(숫자키 1·2·3 보상 선택 등)이 안내에 적혀 있는지 본다</t>
+        </is>
+      </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
           <t>안내에 적힌 조작이 전부 동작하고, 동작하는 조작이 전부 안내에 있다</t>
@@ -4040,7 +4451,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="40.5" customHeight="1">
       <c r="A68" s="11" t="n">
         <v>67</v>
       </c>
@@ -4060,7 +4471,13 @@
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr"/>
-      <c r="F68" s="11" t="inlineStr"/>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>1. 보상방에 들어가 카드가 2장인 것을 확인한다
+2. 패널 안에서 카드가 놓인 위치를 본다
+3. 한쪽이 비어 보이는지 판정하고 캡처한다</t>
+        </is>
+      </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
           <t>카드가 둘이어도 패널 안에서 균형 있게 놓인다</t>
@@ -4093,7 +4510,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="40.5" customHeight="1">
       <c r="A69" s="11" t="n">
         <v>68</v>
       </c>
@@ -4113,7 +4530,13 @@
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr"/>
-      <c r="F69" s="11" t="inlineStr"/>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>1. 한국어로 결과 화면을 띄워 요약 · 안내 · 버튼이 겹치는지 본다
+2. 언어를 English 로 바꾸고 같은 결과 화면을 띄운다
+3. 두 화면을 비교하고 겹치는 쪽을 캡처한다</t>
+        </is>
+      </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
           <t>언어와 무관하게 요약·안내·버튼이 겹치지 않는다</t>
@@ -4146,7 +4569,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="67.5" customHeight="1">
       <c r="A70" s="11" t="n">
         <v>69</v>
       </c>
@@ -4166,7 +4589,15 @@
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr"/>
-      <c r="F70" s="11" t="inlineStr"/>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>1. 적을 때려 타격음을 듣는다
+2. 적 공격에 맞아 피격음을 듣는다
+3. 적을 처치해 사망음을 듣는다
+4. A 로 스왑음을 듣는다
+5. 보상방에서 카드를 골라 보상음을 듣는다</t>
+        </is>
+      </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
           <t>타격·피격·사망·스왑·보상이 각각 난다</t>
@@ -4187,7 +4618,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="27" customHeight="1">
       <c r="A71" s="11" t="n">
         <v>70</v>
       </c>
@@ -4207,7 +4638,12 @@
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr"/>
-      <c r="F71" s="11" t="inlineStr"/>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>1. 시작 화면에서 배경음이 나는지 듣는다
+2. 런을 시작해 전투 중에도 나는지 듣는다</t>
+        </is>
+      </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
           <t>시작 화면과 전투에서 재생된다</t>
@@ -4228,7 +4664,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="40.5" customHeight="1">
       <c r="A72" s="11" t="n">
         <v>71</v>
       </c>
@@ -4248,7 +4684,13 @@
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr"/>
-      <c r="F72" s="11" t="inlineStr"/>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>1. 소리가 나는 상태에서 설정을 연다
+2. 전체 슬라이더를 0 쪽으로 내린다
+3. 슬라이더를 움직이는 동안 소리가 작아지는지 듣는다</t>
+        </is>
+      </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
           <t>설정에서 내리면 즉시 작아진다</t>
@@ -4269,7 +4711,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="40.5" customHeight="1">
       <c r="A73" s="11" t="n">
         <v>72</v>
       </c>
@@ -4293,7 +4735,13 @@
           <t>HP 3</t>
         </is>
       </c>
-      <c r="F73" s="11" t="inlineStr"/>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>1. 한 방에 3보다 큰 피해를 주는 적 공격에 맞는다
+2. HUD 체력 표시를 읽는다
+3. 음수나 빈 값이 보이는지 본다</t>
+        </is>
+      </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
           <t>HP 가 0 에서 멈춘다. 음수가 표시되지 않는다</t>
@@ -4318,7 +4766,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="40.5" customHeight="1">
       <c r="A74" s="11" t="n">
         <v>73</v>
       </c>
@@ -4342,7 +4790,13 @@
           <t>HP 0 · 적 생존</t>
         </is>
       </c>
-      <c r="F74" s="11" t="inlineStr"/>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>1. 적 공격에 맞아 사망한다
+2. 결과 화면이 뜬 뒤에도 남은 적이 공격을 계속하게 둔다
+3. 결과 화면이 두 번 뜨거나 화면이 바뀌는지 본다</t>
+        </is>
+      </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
           <t>결과 화면이 유지되고 두 번 뜨지 않는다</t>
@@ -4367,7 +4821,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="40.5" customHeight="1">
       <c r="A75" s="11" t="n">
         <v>74</v>
       </c>
@@ -4391,7 +4845,13 @@
           <t>HP 30/30</t>
         </is>
       </c>
-      <c r="F75" s="11" t="inlineStr"/>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>1. HUD 체력이 가득한 것을 확인한다
+2. 적 1마리를 처치한다
+3. 체력 표시가 30을 넘는지 본다</t>
+        </is>
+      </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
           <t>30 을 넘지 않는다</t>
@@ -4416,7 +4876,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="40.5" customHeight="1">
       <c r="A76" s="11" t="n">
         <v>75</v>
       </c>
@@ -4440,7 +4900,13 @@
           <t>HP 1 · 공격 중 피격</t>
         </is>
       </c>
-      <c r="F76" s="11" t="inlineStr"/>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>1. F 로 공격을 시작한다
+2. 공격 모션 중에 적 공격을 맞아 사망한다
+3. 사망 후 적에게 피해가 들어가는지 본다</t>
+        </is>
+      </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
           <t>죽은 뒤 공격 판정이 남지 않는다</t>
@@ -4465,7 +4931,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="40.5" customHeight="1">
       <c r="A77" s="11" t="n">
         <v>76</v>
       </c>
@@ -4489,7 +4955,13 @@
           <t>스왑 직후 (쿨타임 3.3초)</t>
         </is>
       </c>
-      <c r="F77" s="11" t="inlineStr"/>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>1. A 로 무기를 바꾼다
+2. 쿨타임 3.3초 동안 A 를 쉬지 않고 연타한다
+3. 게이지가 차는 순간 무기가 한 번만 바뀌는지, 여러 번 연달아 바뀌는지 본다</t>
+        </is>
+      </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
           <t>입력이 쌓였다가 한꺼번에 발동하지 않는다</t>
@@ -4514,7 +4986,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="54" customHeight="1">
       <c r="A78" s="11" t="n">
         <v>77</v>
       </c>
@@ -4538,7 +5010,14 @@
           <t>3타 콤보 2타 진행 중</t>
         </is>
       </c>
-      <c r="F78" s="11" t="inlineStr"/>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>1. F 를 두 번 눌러 2타를 진행시킨다
+2. 2타 모션 중에 A 를 누른다
+3. 공격이 취소되는지 본다
+4. 취소 순간 적에게 피해가 들어가는지 본다 (히트박스가 꺼졌는가)</t>
+        </is>
+      </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
           <t>공격이 취소되고 히트박스가 꺼진다 (GDD 12.4)</t>
@@ -4563,7 +5042,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="54" customHeight="1">
       <c r="A79" s="11" t="n">
         <v>78</v>
       </c>
@@ -4587,7 +5066,14 @@
           <t>점프 정점</t>
         </is>
       </c>
-      <c r="F79" s="11" t="inlineStr"/>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>1. Space 로 점프한다
+2. 가장 높은 지점에서 A 를 누른다
+3. 대시 동안 낙하가 멈추는지 본다
+4. 대시가 끝난 뒤 정상 속도로 떨어지는지 본다</t>
+        </is>
+      </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
           <t>대시 동안 낙하가 멈추고, 끝나면 정상 낙하</t>
@@ -4612,7 +5098,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="40.5" customHeight="1">
       <c r="A80" s="11" t="n">
         <v>79</v>
       </c>
@@ -4636,7 +5122,13 @@
           <t>낙하 지점 위</t>
         </is>
       </c>
-      <c r="F80" s="11" t="inlineStr"/>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>1. 구멍 위로 점프해 떨어지기 시작한다
+2. 낙하 판정이 나기 직전에 A 를 누른다
+3. 복귀 위치가 정상인지 본다 — 공중이나 지형 밖에 서 있지 않은지</t>
+        </is>
+      </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
           <t>복귀 처리와 겹쳐도 위치가 어긋나지 않는다</t>
@@ -4661,7 +5153,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="40.5" customHeight="1">
       <c r="A81" s="11" t="n">
         <v>80</v>
       </c>
@@ -4685,7 +5177,13 @@
           <t>보상 선택 화면</t>
         </is>
       </c>
-      <c r="F81" s="11" t="inlineStr"/>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>1. 보상방 진입 직전에 A 로 스왑해 쿨타임을 걸어 둔다
+2. 보상 선택 화면에서 A 를 누른다
+3. 쿨타임과 무관하게 슬롯이 바뀌는지 본다</t>
+        </is>
+      </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
           <t>쿨타임과 무관하게 슬롯을 바꿀 수 있다</t>
@@ -4710,7 +5208,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="40.5" customHeight="1">
       <c r="A82" s="11" t="n">
         <v>81</v>
       </c>
@@ -4734,7 +5232,13 @@
           <t>HP 30/30</t>
         </is>
       </c>
-      <c r="F82" s="11" t="inlineStr"/>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>1. 체력을 가득 채운 상태로 보상방에 들어간다
+2. 카드가 몇 장인지 센다
+3. 회복 카드가 있는지 본다</t>
+        </is>
+      </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
           <t>회복 카드가 빠지고 2택이 된다</t>
@@ -4759,7 +5263,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="40.5" customHeight="1">
       <c r="A83" s="11" t="n">
         <v>82</v>
       </c>
@@ -4783,7 +5287,13 @@
           <t>선택 화면</t>
         </is>
       </c>
-      <c r="F83" s="11" t="inlineStr"/>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>1. 강화 카드에 적힌 대상 무기와 무기 카드가 버릴 무기를 적어 둔다
+2. A 로 활성 무기를 바꾼다
+3. 두 표시가 함께 바뀌는지 본다</t>
+        </is>
+      </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
           <t>강화 대상과 버릴 무기 표시가 함께 바뀐다</t>
@@ -4808,7 +5318,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="27" customHeight="1">
       <c r="A84" s="11" t="n">
         <v>83</v>
       </c>
@@ -4832,7 +5342,12 @@
           <t>선택 화면</t>
         </is>
       </c>
-      <c r="F84" s="11" t="inlineStr"/>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>1. 숫자키 1 을 눌러 첫 카드가 적용되는지 본다
+2. 다음 보상방에서 2 를, 그 다음에서 3 을 눌러 같은지 본다</t>
+        </is>
+      </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
           <t>1 · 2 · 3 으로도 선택된다</t>
@@ -4857,7 +5372,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="40.5" customHeight="1">
       <c r="A85" s="11" t="n">
         <v>84</v>
       </c>
@@ -4881,7 +5396,13 @@
           <t>선택 화면</t>
         </is>
       </c>
-      <c r="F85" s="11" t="inlineStr"/>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>1. 카드를 고르지 않은 상태로 출구 포탈 위치를 본다
+2. 출구가 열려 있는지 본다
+3. 열려 있으면 밟아 보고 넘어가는지 확인한다</t>
+        </is>
+      </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
           <t>고르기 전에는 출구가 열리지 않는다</t>
@@ -4906,7 +5427,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="40.5" customHeight="1">
       <c r="A86" s="11" t="n">
         <v>85</v>
       </c>
@@ -4930,7 +5451,13 @@
           <t>선택 완료</t>
         </is>
       </c>
-      <c r="F86" s="11" t="inlineStr"/>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>1. 카드를 하나 고른다
+2. 같은 방에서 다른 카드를 클릭하고 숫자키도 눌러 본다
+3. 보상이 두 번 적용되는지 본다 — HUD 강화 수치나 체력으로 확인한다</t>
+        </is>
+      </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
           <t>같은 방에서 두 번 받을 수 없다</t>
@@ -4955,7 +5482,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="54" customHeight="1">
       <c r="A87" s="11" t="n">
         <v>86</v>
       </c>
@@ -4979,7 +5506,14 @@
           <t>강화 +2 상태</t>
         </is>
       </c>
-      <c r="F87" s="11" t="inlineStr"/>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>1. HUD 에서 비활성 무기의 강화 수치를 적어 둔다
+2. 무기 카드를 골라 새 무기를 받는다
+3. 새 무기가 들어간 슬롯이 비활성 쪽인지 본다
+4. 그 슬롯의 강화 수치가 +2 그대로인지 본다</t>
+        </is>
+      </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
           <t>비활성 슬롯이 교체되고 강화 레벨이 승계된다</t>
@@ -5004,7 +5538,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="40.5" customHeight="1">
       <c r="A88" s="11" t="n">
         <v>87</v>
       </c>
@@ -5028,7 +5562,13 @@
           <t>구멍</t>
         </is>
       </c>
-      <c r="F88" s="11" t="inlineStr"/>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>1. 구멍에 떨어져 복귀 위치를 적어 둔다
+2. 같은 구멍에 다시 떨어진다
+3. 이것을 5회 반복하며 복귀 위치와 체력 손실이 매번 같은지 본다</t>
+        </is>
+      </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
           <t>반복해도 매번 복귀하고 규칙이 같다</t>
@@ -5053,7 +5593,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="40.5" customHeight="1">
       <c r="A89" s="11" t="n">
         <v>88</v>
       </c>
@@ -5077,7 +5617,13 @@
           <t>출구에서 피격사</t>
         </is>
       </c>
-      <c r="F89" s="11" t="inlineStr"/>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>1. 적을 유인한 채 출구 포탈 위로 이동한다
+2. 포탈을 밟는 순간 적 공격을 맞아 사망한다
+3. 방 전환과 결과 화면이 겹치는지 본다 — 새 방 배경 위에 결과 화면이 뜨지 않는지</t>
+        </is>
+      </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
           <t>방 전환과 결과 화면이 겹치지 않는다</t>
@@ -5102,7 +5648,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="40.5" customHeight="1">
       <c r="A90" s="11" t="n">
         <v>89</v>
       </c>
@@ -5126,7 +5672,13 @@
           <t>5번째 전투방 클리어</t>
         </is>
       </c>
-      <c r="F90" s="11" t="inlineStr"/>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>1. 5번째 전투방의 적을 전부 처치한다
+2. 출구 포탈을 밟는다
+3. 다음 방이 보상방인지 보스방인지 본다</t>
+        </is>
+      </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
           <t>보상방 없이 보스방으로 간다</t>
@@ -5151,7 +5703,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="40.5" customHeight="1">
       <c r="A91" s="11" t="n">
         <v>90</v>
       </c>
@@ -5175,7 +5727,13 @@
           <t>전투 중</t>
         </is>
       </c>
-      <c r="F91" s="11" t="inlineStr"/>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>1. 전투 중에 R 을 누른다
+2. 런이 다시 시작되는지 본다
+3. Player.log 에 새 시드가 찍히는지 본다</t>
+        </is>
+      </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
           <t>재시작되지 않는다</t>
@@ -5200,7 +5758,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="40.5" customHeight="1">
       <c r="A92" s="11" t="n">
         <v>91</v>
       </c>
@@ -5224,7 +5782,13 @@
           <t>사망 직후</t>
         </is>
       </c>
-      <c r="F92" s="11" t="inlineStr"/>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>1. 결과 화면이 뜬 직후 R 을 빠르게 5회 누른다
+2. 런이 한 번만 시작되는지 본다
+3. Player.log 의 시드가 하나만 찍혔는지 본다</t>
+        </is>
+      </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
           <t>런이 두 번 시작되지 않는다</t>
@@ -5249,7 +5813,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="40.5" customHeight="1">
       <c r="A93" s="11" t="n">
         <v>92</v>
       </c>
@@ -5273,7 +5837,13 @@
           <t>ESC 로 정지</t>
         </is>
       </c>
-      <c r="F93" s="11" t="inlineStr"/>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>1. 전투 중 ESC 로 멈춘다
+2. ← → · Space · F 를 차례로 누른다
+3. 플레이어가 움직이거나 공격하는지 본다</t>
+        </is>
+      </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
           <t>이동 · 점프 · 공격 입력이 무시된다</t>
@@ -5318,7 +5888,7 @@
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr"/>
-      <c r="F94" s="11" t="inlineStr"/>
+      <c r="F94" s="11" t="n"/>
       <c r="G94" s="11" t="inlineStr">
         <is>
           <t>해당 없음 — 전투 씬 설정에는 언어 항목이 없다 (커밋 5578ebc)</t>
@@ -5343,7 +5913,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="40.5" customHeight="1">
       <c r="A95" s="11" t="n">
         <v>94</v>
       </c>
@@ -5367,7 +5937,13 @@
           <t>설정 열림</t>
         </is>
       </c>
-      <c r="F95" s="11" t="inlineStr"/>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>1. 전투 중 설정에서 해상도를 다른 값으로 바꾼다
+2. 설정을 닫고 전투 화면을 본다
+3. HUD 의 체력 · 무기 슬롯 · 게이지가 잘리거나 겹치는지 본다</t>
+        </is>
+      </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
           <t>HUD 가 잘리거나 겹치지 않는다</t>
@@ -5392,7 +5968,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="54" customHeight="1">
       <c r="A96" s="11" t="n">
         <v>95</v>
       </c>
@@ -5416,7 +5992,14 @@
           <t>일시정지 · 설정 열림</t>
         </is>
       </c>
-      <c r="F96" s="11" t="inlineStr"/>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>1. 전투 중 설정에서 해상도를 바꾼다
+2. 설정을 닫지 않은 채로 설정 패널의 위치를 본다
+3. 화면 가운데에 있는지 판정하고 캡처한다
+4. 같은 조작을 시작 화면 설정에서도 해 보고 비교한다</t>
+        </is>
+      </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
           <t>설정창이 화면 가운데에 남는다</t>
@@ -5449,7 +6032,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="54" customHeight="1">
       <c r="A97" s="11" t="n">
         <v>96</v>
       </c>
@@ -5473,7 +6056,14 @@
           <t>볼륨 0 저장 후 재실행</t>
         </is>
       </c>
-      <c r="F97" s="11" t="inlineStr"/>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>1. 설정에서 전체 볼륨을 0 으로 내린다
+2. 게임을 완전히 종료하고 다시 실행한다
+3. 설정 화면의 값이 0 인지 읽는다
+4. 전투에 들어가 소리가 나는지 듣는다</t>
+        </is>
+      </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
           <t>0 이 유지되고 소리가 안 난다</t>
@@ -5498,7 +6088,7 @@
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="40.5" customHeight="1">
       <c r="A98" s="11" t="n">
         <v>97</v>
       </c>
@@ -5522,7 +6112,13 @@
           <t>전투 중 Alt+Tab</t>
         </is>
       </c>
-      <c r="F98" s="11" t="inlineStr"/>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>1. 전투 중 Alt+Tab 으로 다른 창으로 나간다
+2. 10초 뒤 게임 창으로 돌아온다
+3. 플레이어와 적의 움직임이 정상 속도인지 본다 — 빨라지거나 멈춰 있지 않은지</t>
+        </is>
+      </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
           <t>복귀 시 시간이 정상 속도로 돌아온다</t>
@@ -5547,7 +6143,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="40.5" customHeight="1">
       <c r="A99" s="11" t="n">
         <v>98</v>
       </c>
@@ -5571,7 +6167,13 @@
           <t>30분 연속</t>
         </is>
       </c>
-      <c r="F99" s="11" t="inlineStr"/>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>1. 런을 시작하고 30분 연속 플레이하거나 켜 둔다
+2. 30분 뒤 프레임이 떨어졌는지 본다
+3. Player.log 를 열어 예외가 쌓였는지 본다</t>
+        </is>
+      </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
           <t>프레임이 떨어지지 않고 예외가 없다</t>
@@ -5596,7 +6198,7 @@
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="40.5" customHeight="1">
       <c r="A100" s="11" t="n">
         <v>99</v>
       </c>
@@ -5620,7 +6222,13 @@
           <t>해상도 변경</t>
         </is>
       </c>
-      <c r="F100" s="11" t="inlineStr"/>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>1. 설정에서 해상도를 1280×720 으로 바꾼다
+2. 시작 화면 · 도움말 · 설정 · 전투 HUD · 보상 · 결과 화면을 차례로 본다
+3. 잘리거나 화면 밖으로 나간 요소가 있는지 본다</t>
+        </is>
+      </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
           <t>UI 가 잘리지 않는다</t>
@@ -5645,7 +6253,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="40.5" customHeight="1">
       <c r="A101" s="11" t="n">
         <v>100</v>
       </c>
@@ -5665,7 +6273,13 @@
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr"/>
-      <c r="F101" s="11" t="inlineStr"/>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>1. Unity 에디터를 열고 컴파일이 끝나기를 기다린다
+2. Console 창의 Error 필터를 켠다
+3. 비어 있는지 본다</t>
+        </is>
+      </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
           <t>콘솔이 비어 있다</t>
@@ -5686,7 +6300,7 @@
       <c r="L101" s="11" t="inlineStr"/>
       <c r="M101" s="11" t="inlineStr"/>
     </row>
-    <row r="102">
+    <row r="102" ht="40.5" customHeight="1">
       <c r="A102" s="11" t="n">
         <v>101</v>
       </c>
@@ -5706,7 +6320,13 @@
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr"/>
-      <c r="F102" s="11" t="inlineStr"/>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>1. Pixem 에셋의 해당 세 파일을 연다
+2. 파일 맨 위의 using 절이 #if UNITY_EDITOR 안에 있는지 본다
+3. 셋 다 확인한다</t>
+        </is>
+      </c>
       <c r="G102" s="11" t="inlineStr">
         <is>
           <t>세 파일 전부 #if UNITY_EDITOR 안에 있다</t>
@@ -5727,7 +6347,7 @@
       <c r="L102" s="11" t="inlineStr"/>
       <c r="M102" s="11" t="inlineStr"/>
     </row>
-    <row r="103">
+    <row r="103" ht="54" customHeight="1">
       <c r="A103" s="11" t="n">
         <v>102</v>
       </c>
@@ -5747,7 +6367,14 @@
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr"/>
-      <c r="F103" s="11" t="inlineStr"/>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>1. Test Runner 의 EditMode 탭에서 AssetDataTests 를 펼친다
+2. 모든_RoomData_에_roomPrefab_이_있다 · 전투방에는_적_풀과_스폰_수가_있다 ·
+보상방에는_회복량과_무기_풀이_있다 · 모든_WeaponData_에_콤보와_오버라이드_컨트롤러가_있다 ·
+투사체_패턴에는_투사체_프리팹이_있다 다섯을 실행한다</t>
+        </is>
+      </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
           <t>무기·방·패턴 SO 가 전부 누군가에게 참조된다</t>
@@ -5768,7 +6395,7 @@
       <c r="L103" s="11" t="inlineStr"/>
       <c r="M103" s="11" t="inlineStr"/>
     </row>
-    <row r="104">
+    <row r="104" ht="40.5" customHeight="1">
       <c r="A104" s="11" t="n">
         <v>103</v>
       </c>
@@ -5788,7 +6415,13 @@
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr"/>
-      <c r="F104" s="11" t="inlineStr"/>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>1. File &gt; Build Profiles (또는 Build Settings) 를 연다
+2. 씬 목록이 2개인지 센다
+3. 시작 씬이 index 0 인지 본다</t>
+        </is>
+      </c>
       <c r="G104" s="11" t="inlineStr">
         <is>
           <t>시작 씬이 index 0 · 씬 2개</t>
@@ -5809,7 +6442,7 @@
       <c r="L104" s="11" t="inlineStr"/>
       <c r="M104" s="11" t="inlineStr"/>
     </row>
-    <row r="105">
+    <row r="105" ht="54" customHeight="1">
       <c r="A105" s="11" t="n">
         <v>104</v>
       </c>
@@ -5829,7 +6462,14 @@
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr"/>
-      <c r="F105" s="11" t="inlineStr"/>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>1. StageRunner 의 roomCount 와 seed 를 읽는다 — 실서비스 값인지, seed 가 -1 인지
+2. 플레이어의 maxHealth 를 읽는다
+3. 보상방의 healAmount 를 읽는다
+4. 넷 다 실서비스 값인지 확인한다</t>
+        </is>
+      </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
           <t>roomCount · seed · maxHealth · healAmount 가 실서비스 값</t>
@@ -5850,7 +6490,7 @@
       <c r="L105" s="11" t="inlineStr"/>
       <c r="M105" s="11" t="inlineStr"/>
     </row>
-    <row r="106">
+    <row r="106" ht="40.5" customHeight="1">
       <c r="A106" s="11" t="n">
         <v>105</v>
       </c>
@@ -5870,7 +6510,13 @@
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr"/>
-      <c r="F106" s="11" t="inlineStr"/>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>1. Unity 에디터에서 Ctrl+S 로 씬을 저장한다
+2. 터미널에서 git status 를 실행한다
+3. 씬 파일(.unity)이 수정된 채로 남아 있는지 본다</t>
+        </is>
+      </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
           <t>git status 에 미저장 씬이 없다</t>
@@ -5891,7 +6537,7 @@
       <c r="L106" s="11" t="inlineStr"/>
       <c r="M106" s="11" t="inlineStr"/>
     </row>
-    <row r="107">
+    <row r="107" ht="40.5" customHeight="1">
       <c r="A107" s="11" t="n">
         <v>106</v>
       </c>
@@ -5911,7 +6557,13 @@
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr"/>
-      <c r="F107" s="11" t="inlineStr"/>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>1. HealthBar · 결과 화면 · 보상 패널 · 시작 화면의 컴포넌트를 차례로 선택한다
+2. Inspector 에서 참조 필드에 None 이 있는지 본다
+3. 넷 다 확인한다</t>
+        </is>
+      </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
           <t>HealthBar · 결과 · 보상 · 시작 화면 참조가 안 비었다</t>
@@ -5932,7 +6584,7 @@
       <c r="L107" s="11" t="inlineStr"/>
       <c r="M107" s="11" t="inlineStr"/>
     </row>
-    <row r="108">
+    <row r="108" ht="40.5" customHeight="1">
       <c r="A108" s="11" t="n">
         <v>107</v>
       </c>
@@ -5952,7 +6604,13 @@
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr"/>
-      <c r="F108" s="11" t="inlineStr"/>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>1. Edit &gt; Project Settings &gt; Player 를 연다
+2. Version 값을 읽는다
+3. 이번 빌드 번호와 같은지 본다</t>
+        </is>
+      </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
           <t>이번 빌드 번호와 일치한다</t>
@@ -5973,7 +6631,7 @@
       <c r="L108" s="11" t="inlineStr"/>
       <c r="M108" s="11" t="inlineStr"/>
     </row>
-    <row r="109">
+    <row r="109" ht="40.5" customHeight="1">
       <c r="A109" s="11" t="n">
         <v>108</v>
       </c>
@@ -5993,7 +6651,13 @@
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr"/>
-      <c r="F109" s="11" t="inlineStr"/>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>1. 빌드를 실행해 한 런을 완주하고 종료한다
+2. %USERPROFILE%\AppData\LocalLow\&lt;companyName&gt;\WeaponHero\Player.log 를 연다
+3. Exception 이나 Error 가 있는지 찾는다</t>
+        </is>
+      </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
           <t>예외가 없다</t>
@@ -6014,7 +6678,7 @@
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="40.5" customHeight="1">
       <c r="A110" s="11" t="n">
         <v>109</v>
       </c>
@@ -6034,7 +6698,13 @@
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr"/>
-      <c r="F110" s="11" t="inlineStr"/>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>1. TC-BLD-09 와 같은 로그를 연다
+2. Warning 줄을 전부 읽는다
+3. 의도한 구성인데 경고로 남은 것이 있는지 판정한다</t>
+        </is>
+      </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
           <t>의도한 구성이 경고로 남지 않는다</t>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -782,7 +782,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>테스트 스텝은 2026-09-28 초안이다 — 2회전에서 수행하며 확정한다</t>
+          <t>테스트 스텝과 사전 조건은 2026-09-28 초안이다 — 2회전에서 수행하며 확정한다</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,11 @@
           <t>TC-MOVE-01 좌우 이동</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr"/>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 진입 · 적 처치 전</t>
+        </is>
+      </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
           <t>1. ← 를 2초 누른다
@@ -1303,7 +1307,11 @@
           <t>TC-MOVE-02 가변 높이 점프</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr"/>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 진입 · 적 처치 전</t>
+        </is>
+      </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
           <t>1. Space 를 아주 짧게 눌러 떼고 점프 높이를 본다
@@ -1350,7 +1358,11 @@
           <t>TC-MOVE-03 코요테 타임</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr"/>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 진입 · 적 처치 전</t>
+        </is>
+      </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
           <t>1. 발판 끝까지 걸어간다
@@ -1397,7 +1409,11 @@
           <t>TC-MOVE-04 점프 버퍼</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 진입 · 적 처치 전</t>
+        </is>
+      </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
           <t>1. 높은 곳에서 아래로 떨어진다
@@ -1444,7 +1460,11 @@
           <t>TC-MOVE-05 낙하 복귀</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr"/>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 진입 · 적 처치 전</t>
+        </is>
+      </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
           <t>1. 방 안의 구멍(낙하 지점)을 찾아 그 위에 선다
@@ -1491,7 +1511,11 @@
           <t>TC-CMB-01 3타 콤보와 선입력</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 · 적 1마리 이상 생존 · 활성 무기 검</t>
+        </is>
+      </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
           <t>1. 적 앞에서 F 를 누른다
@@ -1539,7 +1563,11 @@
           <t>TC-CMB-02 콤보 타임아웃</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 · 적 1마리 이상 생존 · 활성 무기 검</t>
+        </is>
+      </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
           <t>1. F 로 1타를 낸다
@@ -1587,7 +1615,11 @@
           <t>TC-CMB-03 히트스탑 · 넉백 · 화면 흔들림</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr"/>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 · 적 1마리 이상 생존 · 활성 무기 검</t>
+        </is>
+      </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
           <t>1. 적에게 F 로 한 대 맞힌다
@@ -1634,7 +1666,11 @@
           <t>TC-CMB-04 피격 무적과 깜빡임</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 · 적 1마리 이상 생존 · 활성 무기 검</t>
+        </is>
+      </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
           <t>1. 적 공격에 일부러 한 번 맞는다
@@ -1681,7 +1717,11 @@
           <t>TC-CMB-05 적 둘 사이 연속 피격</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 · 적 1마리 이상 생존 · 활성 무기 검</t>
+        </is>
+      </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
           <t>1. 적 2마리가 함께 있는 방에서 둘 사이로 들어간다
@@ -1729,7 +1769,11 @@
           <t>TC-CMB-06 지상 공격 중 전진</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 · 적 1마리 이상 생존 · 활성 무기 검</t>
+        </is>
+      </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
           <t>1. 지상에서 적과 조금 떨어져 선다
@@ -1776,7 +1820,11 @@
           <t>TC-CMB-07 적 공격이 체력을 깎는다</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 · 적 1마리 이상 생존 · 활성 무기 검</t>
+        </is>
+      </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
           <t>1. HUD 체력 구슬의 현재 상태를 본다
@@ -1823,7 +1871,11 @@
           <t>TC-CMB-08 공중 공격 후 착지</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 전투방 1 · 적 1마리 이상 생존 · 활성 무기 검</t>
+        </is>
+      </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
           <t>1. Space 로 점프한다
@@ -1875,7 +1927,11 @@
           <t>TC-SWAP-01 외형과 모션이 함께 바뀐다</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 무기 2자루 보유 · 스왑 게이지 가득</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>1. 현재 플레이어 외형과 HUD 슬롯 표시를 본다
@@ -1922,7 +1978,11 @@
           <t>TC-SWAP-02 스왑 대시의 무적</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 무기 2자루 보유 · 스왑 게이지 가득</t>
+        </is>
+      </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
           <t>1. 적 공격 예고가 뜨는 것을 보고 그 앞에 선다
@@ -1969,7 +2029,11 @@
           <t>TC-SWAP-03 쿨타임 중 스왑 차단</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 무기 2자루 보유 · 스왑 게이지 가득</t>
+        </is>
+      </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
           <t>1. A 로 무기를 바꾼다
@@ -2016,7 +2080,11 @@
           <t>TC-SWAP-04 스왑 첫 프레임</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 무기 2자루 보유 · 스왑 게이지 가득</t>
+        </is>
+      </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
           <t>1. A 로 무기를 바꾼다
@@ -2063,7 +2131,11 @@
           <t>TC-SWAP-05 무기 이름 표시</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 무기 2자루 보유 · 스왑 게이지 가득</t>
+        </is>
+      </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
           <t>1. HUD 무기 슬롯 두 칸의 글자를 읽는다
@@ -2110,7 +2182,11 @@
           <t>TC-SWAP-06 스왑 중 조작 차단</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작 · 무기 2자루 보유 · 스왑 게이지 가득</t>
+        </is>
+      </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
           <t>1. A 를 눌러 대시를 시작한다
@@ -2157,7 +2233,11 @@
           <t>TC-WPN-01 무기 3종이 다르게 느껴진다</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>검 · 창 · 활을 한 런에서 모두 얻은 상태</t>
+        </is>
+      </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
           <t>1. 검으로 적을 때려 닿는 거리와 타격 간격을 본다
@@ -2205,7 +2285,11 @@
           <t>TC-WPN-02 화살이 맞고 사라진다</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr"/>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>활을 활성 무기로</t>
+        </is>
+      </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
           <t>1. 적을 향해 F 로 화살을 쏜다
@@ -2252,7 +2336,11 @@
           <t>TC-WPN-03 화면 밖 화살이 안 쌓인다</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>활을 활성 무기로 · [에디터] 또는 빌드 · 프레임 표시 수단 준비</t>
+        </is>
+      </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
           <t>1. 적이 없는 방향으로 F 를 3분 이상 연타한다
@@ -2299,7 +2387,11 @@
           <t>TC-WPN-04 창이 빌드에 들어있다</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr"/>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>빌드 실행 · 새 런 시작</t>
+        </is>
+      </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
           <t>1. 빌드를 실행해 새 런을 시작한다
@@ -2346,7 +2438,11 @@
           <t>TC-WPN-05 강화가 적용된다</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr"/>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · Test Runner EditMode</t>
+        </is>
+      </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
           <t>1. Unity 에디터에서 Window &gt; General &gt; Test Runner 를 연다
@@ -2398,7 +2494,11 @@
           <t>TC-WPN-06 강화가 원본 에셋을 오염시키지 않는다</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · Test Runner EditMode</t>
+        </is>
+      </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
           <t>1. Test Runner 의 EditMode 탭에서 WeaponInstanceTests 를 펼친다
@@ -2448,7 +2548,11 @@
           <t>TC-WPN-07 강화 계산의 경계</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · Test Runner EditMode</t>
+        </is>
+      </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
           <t>1. Test Runner 의 EditMode 탭에서 WeaponInstanceTests 를 펼친다
@@ -2498,7 +2602,11 @@
           <t>TC-ENM-01 추격 → 예고 → 공격 → 경직</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr"/>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>전투방 · 돌진형 적 생존</t>
+        </is>
+      </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
           <t>1. 적의 시야 밖에서 천천히 다가간다
@@ -2545,7 +2653,11 @@
           <t>TC-ENM-02 예고 색이 빌드에서 읽힌다</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr"/>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>빌드 실행 · 전투방 · 잡몹 생존</t>
+        </is>
+      </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
           <t>1. 적에게 다가가 공격 예고가 뜨게 한다
@@ -2592,7 +2704,11 @@
           <t>TC-ENM-03 피격이 적 행동을 끊는다</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr"/>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>전투방 · 적 생존</t>
+        </is>
+      </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
           <t>1. 적에게 다가가 예고가 뜨게 한다
@@ -2639,7 +2755,11 @@
           <t>TC-ENM-04 시체가 안 때린다</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>전투방 · 적 생존</t>
+        </is>
+      </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
           <t>1. 적이 공격 모션을 시작하게 만든다
@@ -2686,7 +2806,11 @@
           <t>TC-ENM-05 거리로 패턴이 갈린다</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr"/>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>돌진형 적 생존</t>
+        </is>
+      </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
           <t>1. 적에게 몸이 닿을 만큼 붙어 공격을 받는다
@@ -2734,7 +2858,11 @@
           <t>TC-ENM-06 적 역할이 외형으로 갈린다</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr"/>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>돌진형과 원거리형이 같은 방에 있는 상태</t>
+        </is>
+      </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
           <t>1. 방에 들어간 직후, 적에게 다가가기 전에 화면을 본다
@@ -2785,7 +2913,11 @@
           <t>TC-ENM-07 원거리 적이 물러선다</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr"/>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>원거리형 적 생존</t>
+        </is>
+      </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
           <t>1. 원거리형 적에게 정면으로 걸어간다
@@ -2832,7 +2964,11 @@
           <t>TC-ENM-08 보스 3패턴이 전부 나온다</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr"/>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>보스방 진입 · 체력 여유</t>
+        </is>
+      </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
           <t>1. 보스와 몸이 닿는 거리에서 버틴다 — Smash(0~1.8)
@@ -2880,7 +3016,11 @@
           <t>TC-ENM-09 보스 패턴은 안 끊긴다</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr"/>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>보스방 진입</t>
+        </is>
+      </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
           <t>1. 보스가 패턴을 시작하게 만든다
@@ -2927,7 +3067,11 @@
           <t>TC-ENM-10 패턴 사거리가 구멍 없이 덮인다</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr"/>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · Test Runner EditMode</t>
+        </is>
+      </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
           <t>1. Test Runner 의 EditMode 탭에서 AssetDataTests 를 펼친다
@@ -2978,7 +3122,11 @@
           <t>TC-ENM-11 보스도 예고 색이 읽힌다</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr"/>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>보스방 진입</t>
+        </is>
+      </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
           <t>1. 보스가 패턴을 시작할 때까지 거리를 유지한다
@@ -3037,7 +3185,11 @@
           <t>TC-ROOM-01 방이 연달아 전환된다</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr"/>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>전투방 · 적 처치 전</t>
+        </is>
+      </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
           <t>1. 전투방의 적을 전부 처치한다
@@ -3084,7 +3236,11 @@
           <t>TC-ROOM-02 방 타입이 핸들러로 갈린다</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr"/>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작</t>
+        </is>
+      </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
           <t>1. 전투방에 들어가 무엇이 일어나는지 적는다 — 적이 나오는가
@@ -3132,7 +3288,11 @@
           <t>TC-ROOM-03 카메라가 방을 따라온다</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr"/>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>전투방 클리어 · 출구 열림</t>
+        </is>
+      </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
           <t>1. 출구 포탈을 밟아 다음 방으로 넘어간다
@@ -3181,7 +3341,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>시드 099</t>
+          <t>시드 0~99</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -3288,7 +3448,11 @@
           <t>TC-ROOM-06 타일 PPU</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>전투방</t>
+        </is>
+      </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
           <t>1. 전투방에서 플레이어를 타일 바닥 옆에 세운다
@@ -3337,7 +3501,7 @@
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>시드 099 · roomCount 7</t>
+          <t>시드 0~99 · roomCount 7</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3392,7 +3556,7 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>시드 099</t>
+          <t>시드 0~99</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -3444,7 +3608,11 @@
           <t>TC-RUN-01 10칸 완주</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr"/>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작</t>
+        </is>
+      </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
           <t>1. 새 런을 시작하고 Player.log 에 찍힌 시드를 적어 둔다
@@ -3492,7 +3660,11 @@
           <t>TC-RUN-02 보스 처치 = 클리어</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr"/>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>보스방 진입</t>
+        </is>
+      </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
           <t>1. 보스방에서 보스를 처치한다
@@ -3539,7 +3711,11 @@
           <t>TC-RUN-03 사망 = 런 종료</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr"/>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>새 런 시작</t>
+        </is>
+      </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
           <t>1. 적 공격을 계속 맞아 체력을 0으로 만든다
@@ -3586,7 +3762,11 @@
           <t>TC-RUN-04 R 재시작</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr"/>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>결과 화면 표시 중</t>
+        </is>
+      </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
           <t>1. 결과 화면에서 R 을 누른다
@@ -3633,7 +3813,11 @@
           <t>TC-RUN-05 재시작에 이전 런이 안 남는다</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr"/>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>강화를 받고 무기를 바꾼 뒤 사망한 상태</t>
+        </is>
+      </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
           <t>1. 결과 화면에 적힌 체력 · 무기 · 강화 · 킬 수를 적어 둔다
@@ -3681,7 +3865,11 @@
           <t>TC-RUN-06 보상 3택 1</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr"/>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>체력이 가득하지 않은 상태로 보상방 진입</t>
+        </is>
+      </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
           <t>1. 보상방에 들어가 카드가 몇 장 뜨는지 본다
@@ -3728,7 +3916,11 @@
           <t>TC-RUN-07 가진 무기는 후보에서 빠진다</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr"/>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>검과 활을 든 상태로 보상방 진입</t>
+        </is>
+      </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
           <t>1. 보상방의 무기 카드에 적힌 무기 이름을 읽는다
@@ -3774,7 +3966,11 @@
           <t>TC-RUN-08 보상방 진입이 화면에 드러난다</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr"/>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>보상방 진입 직전</t>
+        </is>
+      </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
           <t>1. 보상방에 들어간다
@@ -3825,7 +4021,11 @@
           <t>TC-RUN-09 처치당 회복</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr"/>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>체력이 가득하지 않은 상태</t>
+        </is>
+      </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
           <t>1. HUD 체력을 보고 현재 값을 적어 둔다
@@ -3872,7 +4072,11 @@
           <t>TC-RUN-10 보상을 고르면 선택 패널이 닫힌다</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr"/>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>보상 선택 화면 표시 중</t>
+        </is>
+      </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
           <t>1. 숫자키 1 로 카드를 고른다
@@ -3931,7 +4135,11 @@
           <t>TC-UI-01 시작 화면 첫 프레임</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr"/>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>게임 완전 종료 상태</t>
+        </is>
+      </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
           <t>1. 게임을 완전히 종료한다
@@ -3982,7 +4190,11 @@
           <t>TC-UI-02 시작 화면 조작</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr"/>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>시작 화면</t>
+        </is>
+      </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
           <t>1. 시작 화면에서 게임 시작을 눌러 런이 시작되는지 본다
@@ -4029,7 +4241,11 @@
           <t>TC-UI-03 ESC 일시정지</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr"/>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>전투 중</t>
+        </is>
+      </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
           <t>1. 전투 중 ESC 를 누른다
@@ -4076,7 +4292,11 @@
           <t>TC-UI-04 설정 5항목</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr"/>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>시작 화면의 설정 (언어 항목이 있는 쪽)</t>
+        </is>
+      </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
           <t>1. 해상도를 다른 값으로 바꾸고 화면이 바뀌는지 본다
@@ -4124,7 +4344,11 @@
           <t>TC-UI-05 설정 저장</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr"/>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>시작 화면</t>
+        </is>
+      </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
           <t>1. 설정에서 해상도 · 볼륨 · 언어를 기본값과 다르게 바꾼다
@@ -4171,7 +4395,11 @@
           <t>TC-UI-06 전투 중 언어 항목</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr"/>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>시작 화면</t>
+        </is>
+      </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
           <t>1. 시작 화면의 설정을 열어 항목을 세어 둔다 — 언어가 있다
@@ -4218,7 +4446,11 @@
           <t>TC-UI-07 영어 안내 문단</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr"/>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>언어 English · 빌드 실행</t>
+        </is>
+      </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
           <t>1. 시작 화면에서 도움말을 연다
@@ -4269,7 +4501,11 @@
           <t>TC-UI-08 HUD</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr"/>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>전투 중 · 무기 2자루</t>
+        </is>
+      </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
           <t>1. 적 공격에 맞고 체력 바가 줄어드는지 본다
@@ -4316,7 +4552,11 @@
           <t>TC-UI-09 결과 화면 로컬라이즈</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr"/>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>언어 English</t>
+        </is>
+      </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
           <t>1. 영어 상태로 런을 시작한다
@@ -4363,7 +4603,11 @@
           <t>TC-UI-10 첫 실행 기본값</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr"/>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>저장된 설정이 없는 상태 · [확인] 레지스트리 정리 필요</t>
+        </is>
+      </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
           <t>1. 레지스트리에서 이 게임의 저장 키를 지운다
@@ -4411,7 +4655,11 @@
           <t>TC-UI-11 안내와 실제 조작이 일치한다</t>
         </is>
       </c>
-      <c r="E67" s="11" t="inlineStr"/>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>시작 화면 · 도움말 열람 가능</t>
+        </is>
+      </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
           <t>1. 도움말의 조작표와 규칙 설명에 적힌 조작을 전부 적어 둔다
@@ -4470,7 +4718,11 @@
           <t>TC-UI-12 보상 카드 정렬</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr"/>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>체력이 가득한 상태로 보상방 진입 (회복 카드가 빠져 2택)</t>
+        </is>
+      </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
           <t>1. 보상방에 들어가 카드가 2장인 것을 확인한다
@@ -4529,7 +4781,11 @@
           <t>TC-UI-13 결과 화면 텍스트 배치</t>
         </is>
       </c>
-      <c r="E69" s="11" t="inlineStr"/>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>런 종료 직후 결과 화면</t>
+        </is>
+      </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
           <t>1. 한국어로 결과 화면을 띄워 요약 · 안내 · 버튼이 겹치는지 본다
@@ -4588,7 +4844,11 @@
           <t>TC-SND-01 효과음 5종</t>
         </is>
       </c>
-      <c r="E70" s="11" t="inlineStr"/>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>효과음 볼륨 1 · 전투 중</t>
+        </is>
+      </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
           <t>1. 적을 때려 타격음을 듣는다
@@ -4637,7 +4897,11 @@
           <t>TC-SND-02 BGM</t>
         </is>
       </c>
-      <c r="E71" s="11" t="inlineStr"/>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>배경음 볼륨 1</t>
+        </is>
+      </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
           <t>1. 시작 화면에서 배경음이 나는지 듣는다
@@ -4683,7 +4947,11 @@
           <t>TC-SND-03 볼륨 반영</t>
         </is>
       </c>
-      <c r="E72" s="11" t="inlineStr"/>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>소리가 나는 상태</t>
+        </is>
+      </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
           <t>1. 소리가 나는 상태에서 설정을 연다
@@ -4732,7 +5000,7 @@
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>HP 3</t>
+          <t>[에디터] HP 3</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -4787,7 +5055,7 @@
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>HP 0 · 적 생존</t>
+          <t>[에디터] HP 1 · 적 2마리 이상 생존</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -4897,7 +5165,7 @@
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>HP 1 · 공격 중 피격</t>
+          <t>[에디터] HP 1</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -5007,7 +5275,7 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>3타 콤보 2타 진행 중</t>
+          <t>3타 콤보 2타 진행 중 · 스왑 게이지 가득</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -5119,7 +5387,7 @@
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>낙하 지점 위</t>
+          <t>낙하 지점(구멍) 위</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
@@ -5174,7 +5442,7 @@
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>보상 선택 화면</t>
+          <t>보상 선택 화면 · 스왑 쿨타임 중</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -5284,7 +5552,7 @@
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>선택 화면</t>
+          <t>보상 선택 화면 · 무기 2자루</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -5339,7 +5607,7 @@
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>선택 화면</t>
+          <t>보상 선택 화면</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -5393,7 +5661,7 @@
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>선택 화면</t>
+          <t>보상 선택 화면 · 아직 고르지 않음</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -5448,7 +5716,7 @@
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>선택 완료</t>
+          <t>보상 선택 완료</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -5503,7 +5771,7 @@
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>강화 +2 상태</t>
+          <t>비활성 무기가 강화 +2 인 상태 · 보상방 진입</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -5559,7 +5827,7 @@
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>구멍</t>
+          <t>낙하 지점이 있는 방</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -5614,7 +5882,7 @@
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>출구에서 피격사</t>
+          <t>[에디터] HP 1 · 적 생존 · 출구 열림</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -5669,7 +5937,7 @@
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>5번째 전투방 클리어</t>
+          <t>5번째 전투방 클리어 직전</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -5779,7 +6047,7 @@
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>사망 직후</t>
+          <t>사망 직후 결과 화면</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -5934,7 +6202,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>설정 열림</t>
+          <t>전투 중 ESC · 설정 열림</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -5989,7 +6257,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>일시정지 · 설정 열림</t>
+          <t>전투 중 ESC · 설정 열림</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -6053,7 +6321,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>볼륨 0 저장 후 재실행</t>
+          <t>전체 볼륨 0 으로 저장</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -6109,7 +6377,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>전투 중 Alt+Tab</t>
+          <t>전투 중 · 창 모드</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -6164,7 +6432,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>30분 연속</t>
+          <t>30분 연속 구동</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -6219,7 +6487,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>해상도 변경</t>
+          <t>해상도 1280×720 으로 변경</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -6272,7 +6540,11 @@
           <t>TC-BLD-01 컴파일 에러 0</t>
         </is>
       </c>
-      <c r="E101" s="11" t="inlineStr"/>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · 빌드 만들기 전</t>
+        </is>
+      </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
           <t>1. Unity 에디터를 열고 컴파일이 끝나기를 기다린다
@@ -6319,7 +6591,11 @@
           <t>TC-BLD-02 Pixem using UnityEditor 가드</t>
         </is>
       </c>
-      <c r="E102" s="11" t="inlineStr"/>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · 빌드 만들기 전</t>
+        </is>
+      </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
           <t>1. Pixem 에셋의 해당 세 파일을 연다
@@ -6366,7 +6642,11 @@
           <t>TC-BLD-03 SO 참조 사슬</t>
         </is>
       </c>
-      <c r="E103" s="11" t="inlineStr"/>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · Test Runner EditMode</t>
+        </is>
+      </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
           <t>1. Test Runner 의 EditMode 탭에서 AssetDataTests 를 펼친다
@@ -6414,7 +6694,11 @@
           <t>TC-BLD-04 빌드 씬 목록</t>
         </is>
       </c>
-      <c r="E104" s="11" t="inlineStr"/>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · 빌드 만들기 전</t>
+        </is>
+      </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
           <t>1. File &gt; Build Profiles (또는 Build Settings) 를 연다
@@ -6461,7 +6745,11 @@
           <t>TC-BLD-05 테스트 값 잔류</t>
         </is>
       </c>
-      <c r="E105" s="11" t="inlineStr"/>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · 빌드 만들기 전</t>
+        </is>
+      </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
           <t>1. StageRunner 의 roomCount 와 seed 를 읽는다 — 실서비스 값인지, seed 가 -1 인지
@@ -6509,7 +6797,11 @@
           <t>TC-BLD-06 씬 저장</t>
         </is>
       </c>
-      <c r="E106" s="11" t="inlineStr"/>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · 빌드 만들기 전</t>
+        </is>
+      </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
           <t>1. Unity 에디터에서 Ctrl+S 로 씬을 저장한다
@@ -6556,7 +6848,11 @@
           <t>TC-BLD-07 UI 배선</t>
         </is>
       </c>
-      <c r="E107" s="11" t="inlineStr"/>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · 빌드 만들기 전</t>
+        </is>
+      </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
           <t>1. HealthBar · 결과 화면 · 보상 패널 · 시작 화면의 컴포넌트를 차례로 선택한다
@@ -6603,7 +6899,11 @@
           <t>TC-BLD-08 bundleVersion</t>
         </is>
       </c>
-      <c r="E108" s="11" t="inlineStr"/>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>Unity 에디터 열림 · 빌드 만들기 전</t>
+        </is>
+      </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
           <t>1. Edit &gt; Project Settings &gt; Player 를 연다
@@ -6650,7 +6950,11 @@
           <t>TC-BLD-09 실행 후 Player.log</t>
         </is>
       </c>
-      <c r="E109" s="11" t="inlineStr"/>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>빌드 실행 후 · Player.log 생성됨</t>
+        </is>
+      </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
           <t>1. 빌드를 실행해 한 런을 완주하고 종료한다
@@ -6697,7 +7001,11 @@
           <t>TC-BLD-10 Player.log 에 오탐 경고가 없다</t>
         </is>
       </c>
-      <c r="E110" s="11" t="inlineStr"/>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>빌드 실행 후 · Player.log 생성됨</t>
+        </is>
+      </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
           <t>1. TC-BLD-09 와 같은 로그를 연다

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -2140,7 +2140,7 @@
         <is>
           <t>1. HUD 무기 슬롯 두 칸의 글자를 읽는다
 2. A 로 바꾼 뒤 다시 읽는다
-3. `검` 처럼 읽히는지, `weapon.sword.name` 같은 키가 보이는지 본다</t>
+3. 검 처럼 읽히는지, weapon.sword.name 같은 키가 보이는지 본다</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>활을 활성 무기로 · [에디터] 또는 빌드 · 프레임 표시 수단 준비</t>
+          <t>활을 활성 무기로 · 에디터 또는 빌드 · 프레임 표시 수단 준비</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -4584,7 +4584,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="54" customHeight="1">
+    <row r="66" ht="40.5" customHeight="1">
       <c r="A66" s="11" t="n">
         <v>65</v>
       </c>
@@ -4605,13 +4605,12 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>저장된 설정이 없는 상태 · [확인] 레지스트리 정리 필요</t>
+          <t>저장된 설정이 없는 상태</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>1. 레지스트리에서 이 게임의 저장 키를 지운다
-(HKCU\Software\&lt;companyName&gt;\WeaponHero)
+          <t>1. 레지스트리에서 HKCU\Software\WeaponHero\WeaponHero 키를 지운다
 2. 게임을 실행하고 설정 화면을 연다
 3. 전체 1 · 배경음 0.8 · 효과음 1 인지 읽는다</t>
         </is>
@@ -5000,7 +4999,7 @@
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>[에디터] HP 3</t>
+          <t>에디터 수행 · HP 3</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5055,7 +5054,7 @@
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>[에디터] HP 1 · 적 2마리 이상 생존</t>
+          <t>에디터 수행 · HP 1 · 적 2마리 이상 생존</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -5165,7 +5164,7 @@
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>[에디터] HP 1</t>
+          <t>에디터 수행 · HP 1</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -5882,7 +5881,7 @@
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>[에디터] HP 1 · 적 생존 · 출구 열림</t>
+          <t>에디터 수행 · HP 1 · 적 생존 · 출구 열림</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -6958,7 +6957,7 @@
       <c r="F109" s="11" t="inlineStr">
         <is>
           <t>1. 빌드를 실행해 한 런을 완주하고 종료한다
-2. %USERPROFILE%\AppData\LocalLow\&lt;companyName&gt;\WeaponHero\Player.log 를 연다
+2. %USERPROFILE%\AppData\LocalLow\WeaponHero\WeaponHero\Player.log 를 연다
 3. Exception 이나 Error 가 있는지 찾는다</t>
         </is>
       </c>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -1130,7 +1130,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>실패 11건 중 4건은 과거 빌드에서 잡아 수정한 것이고, 7건이 이번 회전에서 새로 나왔다.</t>
+          <t>실패 12건 = 과거 빌드에서 잡아 수정한 4건 · 이번 회전 신규 7건 · 이연 1건. 상세는 [결과 보고서] 시트</t>
         </is>
       </c>
     </row>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -15,7 +15,7 @@
     <sheet name="범위 밖 · 이연" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TC 목록'!$A$1:$M$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TC 목록'!$A$1:$N$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -786,6 +786,13 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>[결과] 는 최신 회차다. 1회전 결과는 [1회전 결과] 열에 남겨 같은 줄에서 수정 전후가 보이게 했다 — 집계와 그래프는 [결과] 를 센다</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
@@ -1152,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1163,7 +1170,7 @@
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
@@ -1213,25 +1220,30 @@
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
+          <t>1회전 결과</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>BTS 링크</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>중요도</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>테스트 날짜</t>
         </is>
@@ -1278,11 +1290,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr"/>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J2" s="11" t="inlineStr"/>
       <c r="K2" s="11" t="inlineStr"/>
       <c r="L2" s="11" t="inlineStr"/>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr"/>
+      <c r="N2" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1329,11 +1346,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J3" s="11" t="inlineStr"/>
       <c r="K3" s="11" t="inlineStr"/>
       <c r="L3" s="11" t="inlineStr"/>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="11" t="inlineStr"/>
+      <c r="N3" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1380,11 +1402,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr"/>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J4" s="11" t="inlineStr"/>
       <c r="K4" s="11" t="inlineStr"/>
       <c r="L4" s="11" t="inlineStr"/>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr"/>
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1431,11 +1458,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr"/>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J5" s="11" t="inlineStr"/>
       <c r="K5" s="11" t="inlineStr"/>
       <c r="L5" s="11" t="inlineStr"/>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="11" t="inlineStr"/>
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1482,11 +1514,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr"/>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J6" s="11" t="inlineStr"/>
       <c r="K6" s="11" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1534,11 +1571,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J7" s="11" t="inlineStr"/>
       <c r="K7" s="11" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr"/>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1586,11 +1628,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr"/>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J8" s="11" t="inlineStr"/>
       <c r="K8" s="11" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1637,11 +1684,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
       <c r="L9" s="11" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1688,11 +1740,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr"/>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J10" s="11" t="inlineStr"/>
       <c r="K10" s="11" t="inlineStr"/>
       <c r="L10" s="11" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1740,11 +1797,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr"/>
       <c r="L11" s="11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1791,11 +1853,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J12" s="11" t="inlineStr"/>
       <c r="K12" s="11" t="inlineStr"/>
       <c r="L12" s="11" t="inlineStr"/>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1842,11 +1909,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
       <c r="L13" s="11" t="inlineStr"/>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="M13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1896,13 +1968,18 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
           <t>이연 — 근거가 기록에 있는 미해결</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr"/>
       <c r="K14" s="11" t="inlineStr"/>
       <c r="L14" s="11" t="inlineStr"/>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1949,11 +2026,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J15" s="11" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr"/>
       <c r="L15" s="11" t="inlineStr"/>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2000,11 +2082,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr"/>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J16" s="11" t="inlineStr"/>
       <c r="K16" s="11" t="inlineStr"/>
       <c r="L16" s="11" t="inlineStr"/>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2051,11 +2138,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr"/>
       <c r="L17" s="11" t="inlineStr"/>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2102,11 +2194,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr"/>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J18" s="11" t="inlineStr"/>
       <c r="K18" s="11" t="inlineStr"/>
       <c r="L18" s="11" t="inlineStr"/>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2153,11 +2250,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr"/>
       <c r="L19" s="11" t="inlineStr"/>
-      <c r="M19" s="11" t="inlineStr">
+      <c r="M19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2204,11 +2306,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J20" s="11" t="inlineStr"/>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2256,11 +2363,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr"/>
       <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="M21" s="11" t="inlineStr"/>
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2307,11 +2419,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr"/>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J22" s="11" t="inlineStr"/>
       <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr"/>
-      <c r="M22" s="11" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2358,11 +2475,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr"/>
       <c r="L23" s="11" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="M23" s="11" t="inlineStr"/>
+      <c r="N23" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2409,11 +2531,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr"/>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr"/>
+      <c r="N24" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2463,13 +2590,18 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
           <t>수동 확인 + 자동 테스트</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr"/>
       <c r="L25" s="11" t="inlineStr"/>
-      <c r="M25" s="11" t="inlineStr">
+      <c r="M25" s="11" t="inlineStr"/>
+      <c r="N25" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2517,13 +2649,18 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
           <t>자동 테스트가 판정</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr"/>
       <c r="L26" s="11" t="inlineStr"/>
-      <c r="M26" s="11" t="inlineStr">
+      <c r="M26" s="11" t="inlineStr"/>
+      <c r="N26" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -2571,13 +2708,18 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
           <t>자동 테스트가 판정</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
       <c r="K27" s="11" t="inlineStr"/>
       <c r="L27" s="11" t="inlineStr"/>
-      <c r="M27" s="11" t="inlineStr">
+      <c r="M27" s="11" t="inlineStr"/>
+      <c r="N27" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -2624,11 +2766,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J28" s="11" t="inlineStr"/>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
-      <c r="M28" s="11" t="inlineStr">
+      <c r="M28" s="11" t="inlineStr"/>
+      <c r="N28" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2675,11 +2822,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr"/>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J29" s="11" t="inlineStr"/>
       <c r="K29" s="11" t="inlineStr"/>
       <c r="L29" s="11" t="inlineStr"/>
-      <c r="M29" s="11" t="inlineStr">
+      <c r="M29" s="11" t="inlineStr"/>
+      <c r="N29" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2726,11 +2878,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr"/>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr"/>
       <c r="L30" s="11" t="inlineStr"/>
-      <c r="M30" s="11" t="inlineStr">
+      <c r="M30" s="11" t="inlineStr"/>
+      <c r="N30" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2777,11 +2934,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr"/>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr"/>
       <c r="L31" s="11" t="inlineStr"/>
-      <c r="M31" s="11" t="inlineStr">
+      <c r="M31" s="11" t="inlineStr"/>
+      <c r="N31" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2829,11 +2991,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr"/>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr"/>
       <c r="L32" s="11" t="inlineStr"/>
-      <c r="M32" s="11" t="inlineStr">
+      <c r="M32" s="11" t="inlineStr"/>
+      <c r="N32" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2882,13 +3049,18 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드에서 실패 → 수정됨</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr"/>
       <c r="K33" s="11" t="inlineStr"/>
       <c r="L33" s="11" t="inlineStr"/>
-      <c r="M33" s="11" t="inlineStr">
+      <c r="M33" s="11" t="inlineStr"/>
+      <c r="N33" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2935,11 +3107,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
-      <c r="M34" s="11" t="inlineStr">
+      <c r="M34" s="11" t="inlineStr"/>
+      <c r="N34" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2987,11 +3164,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr"/>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J35" s="11" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr"/>
       <c r="L35" s="11" t="inlineStr"/>
-      <c r="M35" s="11" t="inlineStr">
+      <c r="M35" s="11" t="inlineStr"/>
+      <c r="N35" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3038,11 +3220,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr"/>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
-      <c r="M36" s="11" t="inlineStr">
+      <c r="M36" s="11" t="inlineStr"/>
+      <c r="N36" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3091,13 +3278,18 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
           <t>자동 테스트가 판정</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
       <c r="K37" s="11" t="inlineStr"/>
       <c r="L37" s="11" t="inlineStr"/>
-      <c r="M37" s="11" t="inlineStr">
+      <c r="M37" s="11" t="inlineStr"/>
+      <c r="N37" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -3144,23 +3336,28 @@
           <t>Fail</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr"/>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr"/>
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>#150</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr">
+      <c r="L38" s="11" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="L38" s="11" t="inlineStr">
+      <c r="M38" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M38" s="11" t="inlineStr">
+      <c r="N38" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3207,11 +3404,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr"/>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J39" s="11" t="inlineStr"/>
       <c r="K39" s="11" t="inlineStr"/>
       <c r="L39" s="11" t="inlineStr"/>
-      <c r="M39" s="11" t="inlineStr">
+      <c r="M39" s="11" t="inlineStr"/>
+      <c r="N39" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3259,11 +3461,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr"/>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J40" s="11" t="inlineStr"/>
       <c r="K40" s="11" t="inlineStr"/>
       <c r="L40" s="11" t="inlineStr"/>
-      <c r="M40" s="11" t="inlineStr">
+      <c r="M40" s="11" t="inlineStr"/>
+      <c r="N40" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3310,11 +3517,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr"/>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J41" s="11" t="inlineStr"/>
       <c r="K41" s="11" t="inlineStr"/>
       <c r="L41" s="11" t="inlineStr"/>
-      <c r="M41" s="11" t="inlineStr">
+      <c r="M41" s="11" t="inlineStr"/>
+      <c r="N41" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3363,13 +3575,18 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
           <t>자동 테스트가 판정</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="11" t="inlineStr"/>
       <c r="L42" s="11" t="inlineStr"/>
-      <c r="M42" s="11" t="inlineStr">
+      <c r="M42" s="11" t="inlineStr"/>
+      <c r="N42" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -3417,13 +3634,18 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
           <t>자동 테스트가 판정</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr"/>
       <c r="K43" s="11" t="inlineStr"/>
       <c r="L43" s="11" t="inlineStr"/>
-      <c r="M43" s="11" t="inlineStr">
+      <c r="M43" s="11" t="inlineStr"/>
+      <c r="N43" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -3470,11 +3692,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr"/>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr"/>
       <c r="L44" s="11" t="inlineStr"/>
-      <c r="M44" s="11" t="inlineStr">
+      <c r="M44" s="11" t="inlineStr"/>
+      <c r="N44" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3523,13 +3750,18 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
           <t>자동 테스트가 판정</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr"/>
       <c r="L45" s="11" t="inlineStr"/>
-      <c r="M45" s="11" t="inlineStr">
+      <c r="M45" s="11" t="inlineStr"/>
+      <c r="N45" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -3577,13 +3809,18 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
           <t>자동 테스트가 판정</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr"/>
       <c r="L46" s="11" t="inlineStr"/>
-      <c r="M46" s="11" t="inlineStr">
+      <c r="M46" s="11" t="inlineStr"/>
+      <c r="N46" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -3631,11 +3868,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr"/>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr"/>
       <c r="L47" s="11" t="inlineStr"/>
-      <c r="M47" s="11" t="inlineStr">
+      <c r="M47" s="11" t="inlineStr"/>
+      <c r="N47" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3682,11 +3924,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr"/>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J48" s="11" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr"/>
       <c r="L48" s="11" t="inlineStr"/>
-      <c r="M48" s="11" t="inlineStr">
+      <c r="M48" s="11" t="inlineStr"/>
+      <c r="N48" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3733,11 +3980,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr"/>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr"/>
       <c r="L49" s="11" t="inlineStr"/>
-      <c r="M49" s="11" t="inlineStr">
+      <c r="M49" s="11" t="inlineStr"/>
+      <c r="N49" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3784,11 +4036,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr"/>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr"/>
       <c r="L50" s="11" t="inlineStr"/>
-      <c r="M50" s="11" t="inlineStr">
+      <c r="M50" s="11" t="inlineStr"/>
+      <c r="N50" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3836,11 +4093,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr"/>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr"/>
       <c r="L51" s="11" t="inlineStr"/>
-      <c r="M51" s="11" t="inlineStr">
+      <c r="M51" s="11" t="inlineStr"/>
+      <c r="N51" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3887,11 +4149,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr"/>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr"/>
-      <c r="M52" s="11" t="inlineStr">
+      <c r="M52" s="11" t="inlineStr"/>
+      <c r="N52" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3937,11 +4204,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr"/>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J53" s="11" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr"/>
       <c r="L53" s="11" t="inlineStr"/>
-      <c r="M53" s="11" t="inlineStr">
+      <c r="M53" s="11" t="inlineStr"/>
+      <c r="N53" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3990,13 +4262,18 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드에서 실패 → 수정 후 재확인</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr"/>
       <c r="L54" s="11" t="inlineStr"/>
-      <c r="M54" s="11" t="inlineStr">
+      <c r="M54" s="11" t="inlineStr"/>
+      <c r="N54" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4043,11 +4320,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr"/>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J55" s="11" t="inlineStr"/>
       <c r="K55" s="11" t="inlineStr"/>
       <c r="L55" s="11" t="inlineStr"/>
-      <c r="M55" s="11" t="inlineStr">
+      <c r="M55" s="11" t="inlineStr"/>
+      <c r="N55" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4094,23 +4376,28 @@
           <t>Fail</t>
         </is>
       </c>
-      <c r="I56" s="11" t="inlineStr"/>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr">
         <is>
           <t>#149</t>
         </is>
       </c>
-      <c r="K56" s="11" t="inlineStr">
+      <c r="L56" s="11" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="L56" s="11" t="inlineStr">
+      <c r="M56" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M56" s="11" t="inlineStr">
+      <c r="N56" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4159,13 +4446,18 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드에서 실패 → 수정됨</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr"/>
       <c r="K57" s="11" t="inlineStr"/>
       <c r="L57" s="11" t="inlineStr"/>
-      <c r="M57" s="11" t="inlineStr">
+      <c r="M57" s="11" t="inlineStr"/>
+      <c r="N57" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4212,11 +4504,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr"/>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr"/>
       <c r="L58" s="11" t="inlineStr"/>
-      <c r="M58" s="11" t="inlineStr">
+      <c r="M58" s="11" t="inlineStr"/>
+      <c r="N58" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4263,11 +4560,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I59" s="11" t="inlineStr"/>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J59" s="11" t="inlineStr"/>
       <c r="K59" s="11" t="inlineStr"/>
       <c r="L59" s="11" t="inlineStr"/>
-      <c r="M59" s="11" t="inlineStr">
+      <c r="M59" s="11" t="inlineStr"/>
+      <c r="N59" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4315,11 +4617,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr"/>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J60" s="11" t="inlineStr"/>
       <c r="K60" s="11" t="inlineStr"/>
       <c r="L60" s="11" t="inlineStr"/>
-      <c r="M60" s="11" t="inlineStr">
+      <c r="M60" s="11" t="inlineStr"/>
+      <c r="N60" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4366,11 +4673,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr"/>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J61" s="11" t="inlineStr"/>
       <c r="K61" s="11" t="inlineStr"/>
       <c r="L61" s="11" t="inlineStr"/>
-      <c r="M61" s="11" t="inlineStr">
+      <c r="M61" s="11" t="inlineStr"/>
+      <c r="N61" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4417,11 +4729,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr"/>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J62" s="11" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr"/>
       <c r="L62" s="11" t="inlineStr"/>
-      <c r="M62" s="11" t="inlineStr">
+      <c r="M62" s="11" t="inlineStr"/>
+      <c r="N62" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4470,13 +4787,18 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드에서 실패 → 수정됨</t>
         </is>
       </c>
-      <c r="J63" s="11" t="inlineStr"/>
       <c r="K63" s="11" t="inlineStr"/>
       <c r="L63" s="11" t="inlineStr"/>
-      <c r="M63" s="11" t="inlineStr">
+      <c r="M63" s="11" t="inlineStr"/>
+      <c r="N63" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4523,11 +4845,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr"/>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J64" s="11" t="inlineStr"/>
       <c r="K64" s="11" t="inlineStr"/>
       <c r="L64" s="11" t="inlineStr"/>
-      <c r="M64" s="11" t="inlineStr">
+      <c r="M64" s="11" t="inlineStr"/>
+      <c r="N64" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4574,11 +4901,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr"/>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J65" s="11" t="inlineStr"/>
       <c r="K65" s="11" t="inlineStr"/>
       <c r="L65" s="11" t="inlineStr"/>
-      <c r="M65" s="11" t="inlineStr">
+      <c r="M65" s="11" t="inlineStr"/>
+      <c r="N65" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4625,11 +4957,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr"/>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J66" s="11" t="inlineStr"/>
       <c r="K66" s="11" t="inlineStr"/>
       <c r="L66" s="11" t="inlineStr"/>
-      <c r="M66" s="11" t="inlineStr">
+      <c r="M66" s="11" t="inlineStr"/>
+      <c r="N66" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4676,23 +5013,28 @@
           <t>Fail</t>
         </is>
       </c>
-      <c r="I67" s="11" t="inlineStr"/>
-      <c r="J67" s="11" t="inlineStr">
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr"/>
+      <c r="K67" s="11" t="inlineStr">
         <is>
           <t>#148</t>
         </is>
       </c>
-      <c r="K67" s="11" t="inlineStr">
+      <c r="L67" s="11" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="L67" s="11" t="inlineStr">
+      <c r="M67" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M67" s="11" t="inlineStr">
+      <c r="N67" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4739,23 +5081,28 @@
           <t>Fail</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr"/>
-      <c r="J68" s="11" t="inlineStr">
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr">
         <is>
           <t>#151</t>
         </is>
       </c>
-      <c r="K68" s="11" t="inlineStr">
+      <c r="L68" s="11" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
       </c>
-      <c r="L68" s="11" t="inlineStr">
+      <c r="M68" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M68" s="11" t="inlineStr">
+      <c r="N68" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4802,23 +5149,28 @@
           <t>Fail</t>
         </is>
       </c>
-      <c r="I69" s="11" t="inlineStr"/>
-      <c r="J69" s="11" t="inlineStr">
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr">
         <is>
           <t>#153</t>
         </is>
       </c>
-      <c r="K69" s="11" t="inlineStr">
+      <c r="L69" s="11" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="L69" s="11" t="inlineStr">
+      <c r="M69" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M69" s="11" t="inlineStr">
+      <c r="N69" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4867,11 +5219,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr"/>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J70" s="11" t="inlineStr"/>
       <c r="K70" s="11" t="inlineStr"/>
       <c r="L70" s="11" t="inlineStr"/>
-      <c r="M70" s="11" t="inlineStr">
+      <c r="M70" s="11" t="inlineStr"/>
+      <c r="N70" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4917,11 +5274,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr"/>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J71" s="11" t="inlineStr"/>
       <c r="K71" s="11" t="inlineStr"/>
       <c r="L71" s="11" t="inlineStr"/>
-      <c r="M71" s="11" t="inlineStr">
+      <c r="M71" s="11" t="inlineStr"/>
+      <c r="N71" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4968,11 +5330,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr"/>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J72" s="11" t="inlineStr"/>
       <c r="K72" s="11" t="inlineStr"/>
       <c r="L72" s="11" t="inlineStr"/>
-      <c r="M72" s="11" t="inlineStr">
+      <c r="M72" s="11" t="inlineStr"/>
+      <c r="N72" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5019,15 +5386,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I73" s="11" t="inlineStr"/>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J73" s="11" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr"/>
-      <c r="L73" s="11" t="inlineStr">
+      <c r="L73" s="11" t="inlineStr"/>
+      <c r="M73" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M73" s="11" t="inlineStr">
+      <c r="N73" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5074,15 +5446,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I74" s="11" t="inlineStr"/>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J74" s="11" t="inlineStr"/>
       <c r="K74" s="11" t="inlineStr"/>
-      <c r="L74" s="11" t="inlineStr">
+      <c r="L74" s="11" t="inlineStr"/>
+      <c r="M74" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M74" s="11" t="inlineStr">
+      <c r="N74" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5129,15 +5506,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I75" s="11" t="inlineStr"/>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J75" s="11" t="inlineStr"/>
       <c r="K75" s="11" t="inlineStr"/>
-      <c r="L75" s="11" t="inlineStr">
+      <c r="L75" s="11" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M75" s="11" t="inlineStr">
+      <c r="N75" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -5184,15 +5566,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr"/>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J76" s="11" t="inlineStr"/>
       <c r="K76" s="11" t="inlineStr"/>
-      <c r="L76" s="11" t="inlineStr">
+      <c r="L76" s="11" t="inlineStr"/>
+      <c r="M76" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M76" s="11" t="inlineStr">
+      <c r="N76" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5239,15 +5626,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr"/>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J77" s="11" t="inlineStr"/>
       <c r="K77" s="11" t="inlineStr"/>
-      <c r="L77" s="11" t="inlineStr">
+      <c r="L77" s="11" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M77" s="11" t="inlineStr">
+      <c r="N77" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5295,15 +5687,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I78" s="11" t="inlineStr"/>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J78" s="11" t="inlineStr"/>
       <c r="K78" s="11" t="inlineStr"/>
-      <c r="L78" s="11" t="inlineStr">
+      <c r="L78" s="11" t="inlineStr"/>
+      <c r="M78" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M78" s="11" t="inlineStr">
+      <c r="N78" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5351,15 +5748,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr"/>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J79" s="11" t="inlineStr"/>
       <c r="K79" s="11" t="inlineStr"/>
-      <c r="L79" s="11" t="inlineStr">
+      <c r="L79" s="11" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M79" s="11" t="inlineStr">
+      <c r="N79" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5406,15 +5808,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr"/>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J80" s="11" t="inlineStr"/>
       <c r="K80" s="11" t="inlineStr"/>
-      <c r="L80" s="11" t="inlineStr">
+      <c r="L80" s="11" t="inlineStr"/>
+      <c r="M80" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M80" s="11" t="inlineStr">
+      <c r="N80" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5461,15 +5868,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr"/>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J81" s="11" t="inlineStr"/>
       <c r="K81" s="11" t="inlineStr"/>
-      <c r="L81" s="11" t="inlineStr">
+      <c r="L81" s="11" t="inlineStr"/>
+      <c r="M81" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M81" s="11" t="inlineStr">
+      <c r="N81" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5516,15 +5928,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr"/>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J82" s="11" t="inlineStr"/>
       <c r="K82" s="11" t="inlineStr"/>
-      <c r="L82" s="11" t="inlineStr">
+      <c r="L82" s="11" t="inlineStr"/>
+      <c r="M82" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M82" s="11" t="inlineStr">
+      <c r="N82" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5571,15 +5988,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I83" s="11" t="inlineStr"/>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J83" s="11" t="inlineStr"/>
       <c r="K83" s="11" t="inlineStr"/>
-      <c r="L83" s="11" t="inlineStr">
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M83" s="11" t="inlineStr">
+      <c r="N83" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5625,15 +6047,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I84" s="11" t="inlineStr"/>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J84" s="11" t="inlineStr"/>
       <c r="K84" s="11" t="inlineStr"/>
-      <c r="L84" s="11" t="inlineStr">
+      <c r="L84" s="11" t="inlineStr"/>
+      <c r="M84" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M84" s="11" t="inlineStr">
+      <c r="N84" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5680,15 +6107,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr"/>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J85" s="11" t="inlineStr"/>
       <c r="K85" s="11" t="inlineStr"/>
-      <c r="L85" s="11" t="inlineStr">
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M85" s="11" t="inlineStr">
+      <c r="N85" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5735,15 +6167,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I86" s="11" t="inlineStr"/>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J86" s="11" t="inlineStr"/>
       <c r="K86" s="11" t="inlineStr"/>
-      <c r="L86" s="11" t="inlineStr">
+      <c r="L86" s="11" t="inlineStr"/>
+      <c r="M86" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M86" s="11" t="inlineStr">
+      <c r="N86" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5791,15 +6228,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I87" s="11" t="inlineStr"/>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J87" s="11" t="inlineStr"/>
       <c r="K87" s="11" t="inlineStr"/>
-      <c r="L87" s="11" t="inlineStr">
+      <c r="L87" s="11" t="inlineStr"/>
+      <c r="M87" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M87" s="11" t="inlineStr">
+      <c r="N87" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5846,15 +6288,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I88" s="11" t="inlineStr"/>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J88" s="11" t="inlineStr"/>
       <c r="K88" s="11" t="inlineStr"/>
-      <c r="L88" s="11" t="inlineStr">
+      <c r="L88" s="11" t="inlineStr"/>
+      <c r="M88" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M88" s="11" t="inlineStr">
+      <c r="N88" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5901,15 +6348,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I89" s="11" t="inlineStr"/>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J89" s="11" t="inlineStr"/>
       <c r="K89" s="11" t="inlineStr"/>
-      <c r="L89" s="11" t="inlineStr">
+      <c r="L89" s="11" t="inlineStr"/>
+      <c r="M89" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M89" s="11" t="inlineStr">
+      <c r="N89" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5956,15 +6408,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I90" s="11" t="inlineStr"/>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J90" s="11" t="inlineStr"/>
       <c r="K90" s="11" t="inlineStr"/>
-      <c r="L90" s="11" t="inlineStr">
+      <c r="L90" s="11" t="inlineStr"/>
+      <c r="M90" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M90" s="11" t="inlineStr">
+      <c r="N90" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6011,15 +6468,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I91" s="11" t="inlineStr"/>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J91" s="11" t="inlineStr"/>
       <c r="K91" s="11" t="inlineStr"/>
-      <c r="L91" s="11" t="inlineStr">
+      <c r="L91" s="11" t="inlineStr"/>
+      <c r="M91" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M91" s="11" t="inlineStr">
+      <c r="N91" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6066,15 +6528,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I92" s="11" t="inlineStr"/>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J92" s="11" t="inlineStr"/>
       <c r="K92" s="11" t="inlineStr"/>
-      <c r="L92" s="11" t="inlineStr">
+      <c r="L92" s="11" t="inlineStr"/>
+      <c r="M92" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M92" s="11" t="inlineStr">
+      <c r="N92" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6121,15 +6588,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I93" s="11" t="inlineStr"/>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J93" s="11" t="inlineStr"/>
       <c r="K93" s="11" t="inlineStr"/>
-      <c r="L93" s="11" t="inlineStr">
+      <c r="L93" s="11" t="inlineStr"/>
+      <c r="M93" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M93" s="11" t="inlineStr">
+      <c r="N93" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6168,13 +6640,18 @@
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
           <t>해당 없음 — 그런 조작·상태가 없다</t>
         </is>
       </c>
-      <c r="J94" s="11" t="inlineStr"/>
       <c r="K94" s="11" t="inlineStr"/>
       <c r="L94" s="11" t="inlineStr"/>
-      <c r="M94" s="11" t="inlineStr">
+      <c r="M94" s="11" t="inlineStr"/>
+      <c r="N94" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6221,15 +6698,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I95" s="11" t="inlineStr"/>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J95" s="11" t="inlineStr"/>
       <c r="K95" s="11" t="inlineStr"/>
-      <c r="L95" s="11" t="inlineStr">
+      <c r="L95" s="11" t="inlineStr"/>
+      <c r="M95" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M95" s="11" t="inlineStr">
+      <c r="N95" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6277,23 +6759,28 @@
           <t>Fail</t>
         </is>
       </c>
-      <c r="I96" s="11" t="inlineStr"/>
-      <c r="J96" s="11" t="inlineStr">
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr">
         <is>
           <t>#152</t>
         </is>
       </c>
-      <c r="K96" s="11" t="inlineStr">
+      <c r="L96" s="11" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="L96" s="11" t="inlineStr">
+      <c r="M96" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M96" s="11" t="inlineStr">
+      <c r="N96" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6341,15 +6828,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I97" s="11" t="inlineStr"/>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J97" s="11" t="inlineStr"/>
       <c r="K97" s="11" t="inlineStr"/>
-      <c r="L97" s="11" t="inlineStr">
+      <c r="L97" s="11" t="inlineStr"/>
+      <c r="M97" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M97" s="11" t="inlineStr">
+      <c r="N97" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6396,15 +6888,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I98" s="11" t="inlineStr"/>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J98" s="11" t="inlineStr"/>
       <c r="K98" s="11" t="inlineStr"/>
-      <c r="L98" s="11" t="inlineStr">
+      <c r="L98" s="11" t="inlineStr"/>
+      <c r="M98" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M98" s="11" t="inlineStr">
+      <c r="N98" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6451,15 +6948,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I99" s="11" t="inlineStr"/>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J99" s="11" t="inlineStr"/>
       <c r="K99" s="11" t="inlineStr"/>
-      <c r="L99" s="11" t="inlineStr">
+      <c r="L99" s="11" t="inlineStr"/>
+      <c r="M99" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M99" s="11" t="inlineStr">
+      <c r="N99" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -6506,15 +7008,20 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I100" s="11" t="inlineStr"/>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J100" s="11" t="inlineStr"/>
       <c r="K100" s="11" t="inlineStr"/>
-      <c r="L100" s="11" t="inlineStr">
+      <c r="L100" s="11" t="inlineStr"/>
+      <c r="M100" s="11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M100" s="11" t="inlineStr">
+      <c r="N100" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -6563,13 +7070,18 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드 기록</t>
         </is>
       </c>
-      <c r="J101" s="11" t="inlineStr"/>
       <c r="K101" s="11" t="inlineStr"/>
       <c r="L101" s="11" t="inlineStr"/>
       <c r="M101" s="11" t="inlineStr"/>
+      <c r="N101" s="11" t="inlineStr"/>
     </row>
     <row r="102" ht="40.5" customHeight="1">
       <c r="A102" s="11" t="n">
@@ -6614,13 +7126,18 @@
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드에서 실패 → 수정됨 · 과거 빌드 기록</t>
         </is>
       </c>
-      <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr"/>
       <c r="L102" s="11" t="inlineStr"/>
       <c r="M102" s="11" t="inlineStr"/>
+      <c r="N102" s="11" t="inlineStr"/>
     </row>
     <row r="103" ht="54" customHeight="1">
       <c r="A103" s="11" t="n">
@@ -6666,13 +7183,18 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
           <t>자동 테스트가 판정 · 과거 빌드 기록</t>
         </is>
       </c>
-      <c r="J103" s="11" t="inlineStr"/>
       <c r="K103" s="11" t="inlineStr"/>
       <c r="L103" s="11" t="inlineStr"/>
       <c r="M103" s="11" t="inlineStr"/>
+      <c r="N103" s="11" t="inlineStr"/>
     </row>
     <row r="104" ht="40.5" customHeight="1">
       <c r="A104" s="11" t="n">
@@ -6717,13 +7239,18 @@
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드 기록</t>
         </is>
       </c>
-      <c r="J104" s="11" t="inlineStr"/>
       <c r="K104" s="11" t="inlineStr"/>
       <c r="L104" s="11" t="inlineStr"/>
       <c r="M104" s="11" t="inlineStr"/>
+      <c r="N104" s="11" t="inlineStr"/>
     </row>
     <row r="105" ht="54" customHeight="1">
       <c r="A105" s="11" t="n">
@@ -6769,13 +7296,18 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드 기록</t>
         </is>
       </c>
-      <c r="J105" s="11" t="inlineStr"/>
       <c r="K105" s="11" t="inlineStr"/>
       <c r="L105" s="11" t="inlineStr"/>
       <c r="M105" s="11" t="inlineStr"/>
+      <c r="N105" s="11" t="inlineStr"/>
     </row>
     <row r="106" ht="40.5" customHeight="1">
       <c r="A106" s="11" t="n">
@@ -6820,13 +7352,18 @@
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드 기록</t>
         </is>
       </c>
-      <c r="J106" s="11" t="inlineStr"/>
       <c r="K106" s="11" t="inlineStr"/>
       <c r="L106" s="11" t="inlineStr"/>
       <c r="M106" s="11" t="inlineStr"/>
+      <c r="N106" s="11" t="inlineStr"/>
     </row>
     <row r="107" ht="40.5" customHeight="1">
       <c r="A107" s="11" t="n">
@@ -6871,13 +7408,18 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드 기록</t>
         </is>
       </c>
-      <c r="J107" s="11" t="inlineStr"/>
       <c r="K107" s="11" t="inlineStr"/>
       <c r="L107" s="11" t="inlineStr"/>
       <c r="M107" s="11" t="inlineStr"/>
+      <c r="N107" s="11" t="inlineStr"/>
     </row>
     <row r="108" ht="40.5" customHeight="1">
       <c r="A108" s="11" t="n">
@@ -6922,13 +7464,18 @@
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
           <t>과거 빌드 기록</t>
         </is>
       </c>
-      <c r="J108" s="11" t="inlineStr"/>
       <c r="K108" s="11" t="inlineStr"/>
       <c r="L108" s="11" t="inlineStr"/>
       <c r="M108" s="11" t="inlineStr"/>
+      <c r="N108" s="11" t="inlineStr"/>
     </row>
     <row r="109" ht="40.5" customHeight="1">
       <c r="A109" s="11" t="n">
@@ -6971,11 +7518,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="I109" s="11" t="inlineStr"/>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J109" s="11" t="inlineStr"/>
       <c r="K109" s="11" t="inlineStr"/>
       <c r="L109" s="11" t="inlineStr"/>
-      <c r="M109" s="11" t="inlineStr">
+      <c r="M109" s="11" t="inlineStr"/>
+      <c r="N109" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -7022,30 +7574,35 @@
           <t>Fail</t>
         </is>
       </c>
-      <c r="I110" s="11" t="inlineStr"/>
-      <c r="J110" s="11" t="inlineStr">
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr"/>
+      <c r="K110" s="11" t="inlineStr">
         <is>
           <t>#154</t>
         </is>
       </c>
-      <c r="K110" s="11" t="inlineStr">
+      <c r="L110" s="11" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
       </c>
-      <c r="L110" s="11" t="inlineStr">
+      <c r="M110" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M110" s="11" t="inlineStr">
+      <c r="N110" s="11" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M110"/>
+  <autoFilter ref="A1:N110"/>
   <conditionalFormatting sqref="H2:H110">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Fail"</formula>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -7080,8 +7080,12 @@
       </c>
       <c r="K101" s="11" t="inlineStr"/>
       <c r="L101" s="11" t="inlineStr"/>
-      <c r="M101" s="11" t="inlineStr"/>
-      <c r="N101" s="11" t="inlineStr"/>
+      <c r="M101" s="11" t="n"/>
+      <c r="N101" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="40.5" customHeight="1">
       <c r="A102" s="11" t="n">
@@ -7121,7 +7125,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -7136,8 +7140,12 @@
       </c>
       <c r="K102" s="11" t="inlineStr"/>
       <c r="L102" s="11" t="inlineStr"/>
-      <c r="M102" s="11" t="inlineStr"/>
-      <c r="N102" s="11" t="inlineStr"/>
+      <c r="M102" s="11" t="n"/>
+      <c r="N102" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="54" customHeight="1">
       <c r="A103" s="11" t="n">
@@ -7249,8 +7257,12 @@
       </c>
       <c r="K104" s="11" t="inlineStr"/>
       <c r="L104" s="11" t="inlineStr"/>
-      <c r="M104" s="11" t="inlineStr"/>
-      <c r="N104" s="11" t="inlineStr"/>
+      <c r="M104" s="11" t="n"/>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="54" customHeight="1">
       <c r="A105" s="11" t="n">
@@ -7306,8 +7318,12 @@
       </c>
       <c r="K105" s="11" t="inlineStr"/>
       <c r="L105" s="11" t="inlineStr"/>
-      <c r="M105" s="11" t="inlineStr"/>
-      <c r="N105" s="11" t="inlineStr"/>
+      <c r="M105" s="11" t="n"/>
+      <c r="N105" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="40.5" customHeight="1">
       <c r="A106" s="11" t="n">
@@ -7362,8 +7378,12 @@
       </c>
       <c r="K106" s="11" t="inlineStr"/>
       <c r="L106" s="11" t="inlineStr"/>
-      <c r="M106" s="11" t="inlineStr"/>
-      <c r="N106" s="11" t="inlineStr"/>
+      <c r="M106" s="11" t="n"/>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="40.5" customHeight="1">
       <c r="A107" s="11" t="n">
@@ -7459,7 +7479,7 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -7474,8 +7494,12 @@
       </c>
       <c r="K108" s="11" t="inlineStr"/>
       <c r="L108" s="11" t="inlineStr"/>
-      <c r="M108" s="11" t="inlineStr"/>
-      <c r="N108" s="11" t="inlineStr"/>
+      <c r="M108" s="11" t="n"/>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="40.5" customHeight="1">
       <c r="A109" s="11" t="n">

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -4441,7 +4441,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -4459,7 +4459,7 @@
       <c r="M57" s="11" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -4800,7 +4800,7 @@
       <c r="M63" s="11" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>TC-EDGE-27 1280×720</t>
+          <t>TC-EDGE-27 1600×900</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -1301,7 +1301,7 @@
       <c r="M2" s="11" t="inlineStr"/>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       <c r="M3" s="11" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       <c r="M4" s="11" t="inlineStr"/>
       <c r="N4" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       <c r="M5" s="11" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       <c r="M6" s="11" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       <c r="M7" s="11" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       <c r="M8" s="11" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       <c r="M9" s="11" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       <c r="M10" s="11" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       <c r="M11" s="11" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       <c r="M12" s="11" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="M13" s="11" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       <c r="M14" s="11" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       <c r="M15" s="11" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       <c r="M16" s="11" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       <c r="M17" s="11" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>TC-SWAP-04 스왑 첫 프레임</t>
+          <t>TC-SWAP-04 스왑 순간의 잔상</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -2205,7 +2205,7 @@
       <c r="M18" s="11" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       <c r="M19" s="11" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       <c r="M20" s="11" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       <c r="M44" s="11" t="inlineStr"/>
       <c r="N44" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       <c r="M58" s="11" t="inlineStr"/>
       <c r="N58" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       <c r="M60" s="11" t="inlineStr"/>
       <c r="N60" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       <c r="M61" s="11" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       <c r="M64" s="11" t="inlineStr"/>
       <c r="N64" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       <c r="M66" s="11" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       <c r="M70" s="11" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
       <c r="M71" s="11" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
       <c r="M72" s="11" t="inlineStr"/>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="N80" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="N88" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="N97" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="N100" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -2374,7 +2374,7 @@
       <c r="M21" s="11" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       <c r="M23" s="11" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       <c r="M24" s="11" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       <c r="M28" s="11" t="inlineStr"/>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       <c r="M29" s="11" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       <c r="M30" s="11" t="inlineStr"/>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       <c r="M31" s="11" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       <c r="M32" s="11" t="inlineStr"/>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -3062,7 +3062,7 @@
       <c r="M33" s="11" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       <c r="M39" s="11" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       <c r="M40" s="11" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       <c r="M41" s="11" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       <c r="M54" s="11" t="inlineStr"/>
       <c r="N54" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       <c r="M55" s="11" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="N90" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="N91" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -2603,7 +2603,7 @@
       <c r="M25" s="11" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       <c r="M52" s="11" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       <c r="M53" s="11" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="N56" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="N68" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="N82" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="N84" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="N86" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -3175,7 +3175,7 @@
       <c r="M35" s="11" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       <c r="M36" s="11" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       <c r="M47" s="11" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       <c r="M48" s="11" t="inlineStr"/>
       <c r="N48" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>TC-UI-03 ESC 일시정지</t>
+          <t>TC-UI-03 ESC 일시정지와 재개</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -4565,13 +4565,25 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J59" s="11" t="inlineStr"/>
-      <c r="K59" s="11" t="inlineStr"/>
-      <c r="L59" s="11" t="inlineStr"/>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>#165 닫기 버튼으로 닫으면 timeScale 이 0 에 묶인다</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>#165</t>
+        </is>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
       <c r="M59" s="11" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4752,7 @@
       <c r="M62" s="11" t="inlineStr"/>
       <c r="N62" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6597,7 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -6593,9 +6605,21 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J93" s="11" t="inlineStr"/>
-      <c r="K93" s="11" t="inlineStr"/>
-      <c r="L93" s="11" t="inlineStr"/>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>#166 A 가 먹힌다</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>#166</t>
+        </is>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
           <t>High</t>
@@ -6603,7 +6627,7 @@
       </c>
       <c r="N93" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6677,7 @@
       <c r="M94" s="11" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6737,7 @@
       </c>
       <c r="N95" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6780,7 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -6782,7 +6806,7 @@
       </c>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6927,7 @@
       </c>
       <c r="N98" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -3991,7 +3991,7 @@
       <c r="M49" s="11" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       <c r="M50" s="11" t="inlineStr"/>
       <c r="N50" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       <c r="M51" s="11" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
       <c r="M65" s="11" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="N92" s="11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -2662,7 +2662,7 @@
       <c r="M26" s="11" t="inlineStr"/>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       <c r="M27" s="11" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       <c r="M37" s="11" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       <c r="M42" s="11" t="inlineStr"/>
       <c r="N42" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       <c r="M43" s="11" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       <c r="M45" s="11" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       <c r="M46" s="11" t="inlineStr"/>
       <c r="N46" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,11 @@
       <c r="K103" s="11" t="inlineStr"/>
       <c r="L103" s="11" t="inlineStr"/>
       <c r="M103" s="11" t="inlineStr"/>
-      <c r="N103" s="11" t="inlineStr"/>
+      <c r="N103" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="40.5" customHeight="1">
       <c r="A104" s="11" t="n">

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>docs/qa/test-cases.md · docs/qa/test-run-log.md · docs/qa/test-plan.md · docs/qa/test-steps-draft.md</t>
+          <t>docs/qa/test-cases.md · docs/qa/test-run-log.md · docs/qa/test-plan.md · docs/qa/test-steps.md</t>
         </is>
       </c>
     </row>
@@ -779,13 +779,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>테스트 스텝과 사전 조건은 2026-09-28 초안이다 — 2회전에서 수행하며 확정한다</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -1137,7 +1130,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>실패 12건 = 과거 빌드에서 잡아 수정한 4건 · 이번 회전 신규 7건 · 이연 1건. 상세는 [결과 보고서] 시트</t>
+          <t>실패 5건 = 미수정 결함 3건(#165 #166 #164) · 안 고치기로 판단한 1건(#151) · 이연 1건(#143). 1회전 12건은 [1회전 결과] 열에 있다. 상세는 [결과 보고서] 시트</t>
         </is>
       </c>
     </row>
@@ -2179,9 +2172,9 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>1. A 로 무기를 바꾼다
-2. 교체 순간을 영상으로 녹화하거나 연속 캡처한다
-3. 프레임을 넘겨 보며 옛 무기 그림이 한 프레임이라도 남는지 본다</t>
+          <t>1. 적 앞에서 A 로 무기를 바꾼다
+2. 교체 순간 플레이어를 본다
+3. 옛 무기 그림이 번쩍이는 것이 눈에 띄는지 본다</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -3672,14 +3665,14 @@
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>전투방</t>
+          <t>에디터 수행</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>1. 전투방에서 플레이어를 타일 바닥 옆에 세운다
-2. 캡처해서 타일 한 칸과 캐릭터의 픽셀 크기를 비교한다
-3. 같은 해상도(PPU 32)로 보이는지 본다</t>
+          <t>1. 타일셋 스프라이트를 선택해 Inspector 의 Pixels Per Unit 을 읽는다
+2. 캐릭터 스프라이트도 같은 값인지 읽는다
+3. 둘이 32 로 같은지 본다</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -5378,14 +5371,14 @@
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>에디터 수행 · HP 3</t>
+          <t>HP 9 이하 · 보스방</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>1. 한 방에 3보다 큰 피해를 주는 적 공격에 맞는다
-2. HUD 체력 표시를 읽는다
-3. 음수나 빈 값이 보이는지 본다</t>
+          <t>1. 적 공격을 맞아 HP 를 한 자리로 깎는다 — 처치하면 1 회복하므로 죽이지 말고 유인한다
+2. 오우거 돌진(피해 10)에 맞는다
+3. HUD 체력 표시와 결과 화면의 HP 를 읽는다 — 음수나 빈 값이 보이는지 본다</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5438,7 +5431,7 @@
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>에디터 수행 · HP 1 · 적 2마리 이상 생존</t>
+          <t>한 방에 죽을 HP · 적 2마리 이상 생존</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -5558,7 +5551,7 @@
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>에디터 수행 · HP 1</t>
+          <t>한 방에 죽을 HP</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -6319,7 +6312,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="40.5" customHeight="1">
+    <row r="89">
       <c r="A89" s="11" t="n">
         <v>88</v>
       </c>
@@ -6338,18 +6331,8 @@
           <t>TC-EDGE-17 포탈 위에서 사망</t>
         </is>
       </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>에디터 수행 · HP 1 · 적 생존 · 출구 열림</t>
-        </is>
-      </c>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>1. 적을 유인한 채 출구 포탈 위로 이동한다
-2. 포탈을 밟는 순간 적 공격을 맞아 사망한다
-3. 방 전환과 결과 화면이 겹치는지 본다 — 새 방 배경 위에 결과 화면이 뜨지 않는지</t>
-        </is>
-      </c>
+      <c r="E89" s="11" t="n"/>
+      <c r="F89" s="11" t="n"/>
       <c r="G89" s="11" t="inlineStr">
         <is>
           <t>방 전환과 결과 화면이 겹치지 않는다</t>
@@ -6527,7 +6510,7 @@
         <is>
           <t>1. 결과 화면이 뜬 직후 R 을 빠르게 5회 누른다
 2. 런이 한 번만 시작되는지 본다
-3. Player.log 의 시드가 하나만 찍혔는지 본다</t>
+3. Player.log 의 런 시작 이 몇 줄인지 센다 — 런 종료 와 교대해야 한다</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -6987,7 +6970,7 @@
       </c>
       <c r="N99" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7012,12 +6995,12 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>해상도 1280×720 으로 변경</t>
+          <t>해상도 1600×900 으로 변경</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>1. 설정에서 해상도를 1280×720 으로 바꾼다
+          <t>1. 설정에서 해상도를 1600×900 으로 바꾼다
 2. 시작 화면 · 도움말 · 설정 · 전투 HUD · 보상 · 결과 화면을 차례로 본다
 3. 잘리거나 화면 밖으로 나간 요소가 있는지 본다</t>
         </is>
@@ -7413,7 +7396,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="40.5" customHeight="1">
+    <row r="107" ht="54" customHeight="1">
       <c r="A107" s="11" t="n">
         <v>106</v>
       </c>
@@ -7434,14 +7417,15 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Unity 에디터 열림 · 빌드 만들기 전</t>
+          <t>한 런을 끝까지 돈 Player.log</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>1. HealthBar · 결과 화면 · 보상 패널 · 시작 화면의 컴포넌트를 차례로 선택한다
-2. Inspector 에서 참조 필드에 None 이 있는지 본다
-3. 넷 다 확인한다</t>
+          <t>1. 시작 화면 · 전투 · 보상 · 결과 화면을 한 번씩 지나는 런을 돈다
+2. 정상 종료한다 — 강제 종료하면 종료 구간이 안 남는다
+3. Player.log 에서 "미지정" · "비어 있다" · "없다" 를 찾는다
+4. 한 줄도 없으면 통과</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -7467,7 +7451,11 @@
       <c r="K107" s="11" t="inlineStr"/>
       <c r="L107" s="11" t="inlineStr"/>
       <c r="M107" s="11" t="inlineStr"/>
-      <c r="N107" s="11" t="inlineStr"/>
+      <c r="N107" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="40.5" customHeight="1">
       <c r="A108" s="11" t="n">
@@ -7581,7 +7569,7 @@
       <c r="M109" s="11" t="inlineStr"/>
       <c r="N109" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7611,7 @@
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -7649,7 +7637,7 @@
       </c>
       <c r="N110" s="11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -789,7 +789,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>결과 집계</t>
+          <t>[결과] 는 2회전(2026-10-03~04) 판정이다. 회전이 끝난 뒤 고친 것은 결과 열을 덮지 않고 [비고] 에 적는다 — 그 회차가 무엇을 찾았는지가 사라지기 때문이다. 현재 상태는 TC-UI-03 · TC-BLD-08 이 수정·확인되어 미수정 결함은 2건이다</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>#165 닫기 버튼으로 닫으면 timeScale 이 0 에 묶인다</t>
+          <t>#165 닫기 버튼으로 닫으면 timeScale 이 0 에 묶인다 → 2회전 뒤 수정·빌드 확인 (2026-10-04)</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr">
@@ -7505,10 +7505,14 @@
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>과거 빌드 기록</t>
-        </is>
-      </c>
-      <c r="K108" s="11" t="inlineStr"/>
+          <t>bundleVersion 이 0.4 였다 → 2회전 뒤 1.1 로 올리고 빌드 확인 (2026-10-04)</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>#164</t>
+        </is>
+      </c>
       <c r="L108" s="11" t="inlineStr"/>
       <c r="M108" s="11" t="n"/>
       <c r="N108" s="11" t="inlineStr">

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -1164,10 +1164,11 @@
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2179,7 +2180,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>교체 순간 옛 무기 그림이 한 프레임도 안 보인다</t>
+          <t>교체 직후 옛 무기 잔상이 눈에 띄지 않는다</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -3261,7 +3262,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>보스 010 · 근접에는 높이 제한이 있다</t>
+          <t>보스 0~10 · 근접에는 높이 제한이 있다</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -4545,7 +4546,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>전투 중 ESC 로 멈추고 설정이 열린다</t>
+          <t>멈추고 설정이 열린다. ESC 로든 닫기 버튼으로든 닫으면 재개된다</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -6575,7 +6576,7 @@
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>이동 · 점프 · 공격 입력이 무시된다</t>
+          <t>어떤 조작도 게임 상태를 바꾸지 않는다 — 이동·점프·공격·무기 교체</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -7485,7 +7486,7 @@
         <is>
           <t>1. Edit &gt; Project Settings &gt; Player 를 연다
 2. Version 값을 읽는다
-3. 이번 빌드 번호와 같은지 본다</t>
+3. 이번 회전 문서가 부르는 이름(test-plan.md · 수행 계획의 "대상 빌드 vN.N")과 같은지 본다</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">

--- a/docs/qa/WeaponHero_TC.xlsx
+++ b/docs/qa/WeaponHero_TC.xlsx
@@ -679,7 +679,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>WeaponHero — 1회전 테스트 결과</t>
+          <t>WeaponHero — 1차 · 2차 테스트 결과</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1차 제출 빌드의 회귀 확인과 경계·비정상 흐름 검증</t>
+          <t>1차 제출 빌드의 회귀 확인과 경계·비정상 흐름 검증 → 2차는 수정분 회귀와 테스트 스텝 확정</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>v1.0 (2026-09-03 제출본) · Windows x64</t>
+          <t>1차 v1.0 (2026-09-03 제출본) · 2차 v1.1 (결함 7건 수정 반영) · Windows x64</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 ~ 2026-09-24 · 세션 8회</t>
+          <t>1차 2026-09-23~24 세션 8회 · 2차 2026-10-03~04 세션 9회</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>docs/qa/test-cases.md · docs/qa/test-run-log.md · docs/qa/test-plan.md · docs/qa/test-steps.md</t>
+          <t>docs/qa/test-cases.md · test-run-log.md · test-run-log-2nd.md · test-plan.md · test-steps.md · test-report.md · test-report-2nd.md</t>
         </is>
       </c>
     </row>
@@ -775,21 +775,21 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[결과] 는 최신 회차다. 1회전 결과는 [1회전 결과] 열에 남겨 같은 줄에서 수정 전후가 보이게 했다 — 집계와 그래프는 [결과] 를 센다</t>
+          <t>[결과] 는 최신 차수다. 1차 결과는 [1차 결과] 열에 남겨 같은 줄에서 수정 전후가 보이게 했다 — 집계와 그래프는 [결과] 를 센다</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>[결과] 는 2회전(2026-10-03~04) 판정이다. 회전이 끝난 뒤 고친 것은 결과 열을 덮지 않고 [비고] 에 적는다 — 그 회차가 무엇을 찾았는지가 사라지기 때문이다. 현재 상태는 TC-UI-03 · TC-BLD-08 이 수정·확인되어 미수정 결함은 2건이다</t>
+          <t>[결과] 는 2차(2026-10-03~04) 판정이다. 차수가 끝난 뒤 고친 것은 결과 열을 덮지 않고 [비고] 에 적는다 — 그 차수가 무엇을 찾았는지가 사라지기 때문이다. 현재 상태는 TC-UI-03 · TC-BLD-08 이 수정·확인되어 미수정 결함은 2건이다</t>
         </is>
       </c>
     </row>
@@ -1123,14 +1123,14 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>이번 회전 신규 결함 7건 — 상세는 [결함] 시트</t>
+          <t>찾은 결함 10건 (1차 7 · 2차 3) — 상세는 [결함] 시트</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>실패 5건 = 미수정 결함 3건(#165 #166 #164) · 안 고치기로 판단한 1건(#151) · 이연 1건(#143). 1회전 12건은 [1회전 결과] 열에 있다. 상세는 [결과 보고서] 시트</t>
+          <t>실패 5건 = 미수정 결함 2건(#166 #143) · 안 고치기로 판단한 1건(#151) · 수정 후 확인 2건(#165 #164 — [비고] 참고). 1차 12건은 [1차 결과] 열에 있다</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
-          <t>1회전 결과</t>
+          <t>1차 결과</t>
         </is>
       </c>
       <c r="J1" s="5" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>#165 닫기 버튼으로 닫으면 timeScale 이 0 에 묶인다 → 2회전 뒤 수정·빌드 확인 (2026-10-04)</t>
+          <t>#165 닫기 버튼으로 닫으면 timeScale 이 0 에 묶인다 → 2차 뒤 수정·빌드 확인 (2026-10-04)</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>bundleVersion 이 0.4 였다 → 2회전 뒤 1.1 로 올리고 빌드 확인 (2026-10-04)</t>
+          <t>bundleVersion 이 0.4 였다 → 2차 뒤 1.1 로 올리고 빌드 확인 (2026-10-04)</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr">
@@ -7688,14 +7688,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>1회전 테스트 결과 보고서</t>
+          <t>테스트 결과 보고서 — 1차 · 2차</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>대상 빌드 v1.0 (2026-09-03 제출본) · 수행 2026-09-23 ~ 09-24 · 세션 8회</t>
+          <t>1차 v1.0 (2026-09-03 제출본) 09-23~24 세션 8회 · 2차 v1.1 (결함 7건 수정) 10-03~04 세션 9회</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 ~ 2026-09-24</t>
+          <t>1차 2026-09-23 ~ 09-24 · 2차 2026-10-03 ~ 10-04</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>v1.0 · Windows x64</t>
+          <t>1차 v1.0 · 2차 v1.1 · Windows x64</t>
         </is>
       </c>
     </row>
@@ -7786,14 +7786,14 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>수동(빌드) + 수동(에디터) + 자동(EditMode 21개)</t>
+          <t>수동(빌드) + 수동(에디터) + 자동(유니티 에디터 테스트 21개)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>영역별 테스트 요약</t>
+          <t>영역별 테스트 요약 — 2차 기준 (1차는 [TC 목록] 의 [1차 결과] 열)</t>
         </is>
       </c>
     </row>
@@ -8168,91 +8168,91 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>시작 시 △ 6건이 전부 해소됐다. 확인 못 한 항목을 통과로 적지 않는 것이 이 표의 규칙이므로, 0 은 모든 항목에 대해 봤거나 못 본 이유가 적혀 있다는 뜻이다.</t>
+          <t>두 차수 모두 0 이다. 확인 못 한 항목을 통과로 적지 않는 것이 이 표의 규칙이므로, 0 은 모든 항목에 대해 봤거나 못 본 이유가 적혀 있다는 뜻이다.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Major 셋의 공통점</t>
+          <t>회귀 7건</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>#153 #150 #149 는 전부 "동작은 하는데 읽을 수 없다"에 해당한다. #150 은 보스 패턴이 안 끊기므로 예고가 유일한 회피 신호라는 점에서 특히 무겁다.</t>
+          <t>1차에서 고친 7건이 전부 통과했다. #150 은 빌드 캡처에서 픽셀을 재어 확인했다 — RGB(90,197,79) → (90,197,17). 에디터에서 쟀던 값과 같다.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>#149 가 Critical 이 아닌 이유</t>
+          <t>1차 판정이 뒤집힌 셋</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>TC-EDGE-14(재선택 불가)가 통과해, 패널이 남아도 보상이 두 번 적용되지 않는 것을 확인했다.</t>
+          <t>TC-EDGE-27 은 빌드에 없는 해상도를 적어 뒀고, TC-BLD-08 은 값을 안 보고 통과로 넘겼다. TC-EDGE-17 은 선행 조건 자체를 만들 수 없어 N/A 로 내렸다 — 수행자가 성실해도 못 막는 종류다.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Trivial 을 남긴 이유</t>
+          <t>기대 결과를 넓힌 둘</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>#154 는 매 실행마다 뜨는 오탐 경고다. 두면 진짜 배선 누락이 같은 줄에 섞인다 — W3 에서 HurtBox.health 를 놓친 것이 그 종류였다.</t>
+          <t>TC-UI-03 · TC-EDGE-21 은 문구가 좁아 1차에 통과했다. 넓히자 #165 · #166 이 나왔다. 기대 결과에 조작을 열거하면 열거된 것만 확인된다.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>과거 수정분 4건</t>
+          <t>신규 결함 3건</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>TC-UI-01 · UI-07 · ROOM-04 · RUN-08 의 수정이 유지되는 것을 확인했다. ROOM-04 는 자동 테스트로 승격돼 사람이 다시 안 본다.</t>
+          <t>#165 Major · #166 Minor · #167 Trivial. 셋 다 수행 목록이 아니라 회귀를 보는 중에 나왔다. #165 는 고쳐 빌드에서 확인했다.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>이연 1건</t>
+          <t>안 고치기로 한 것</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>TC-CMB-08 은 재현됐고 고치지 않는다. 범위가 1차에 없다는 근거가 기록에 있고, 이번 수행의 목적은 그 판단이 유효한지 보는 것이었다.</t>
+          <t>#151 · #167 은 동작이 아니라 보기 문제라 근거를 적고 닫았다. #143 은 고치면 밸런스가 바뀌는데 확인할 차수가 없어 되살아나는 조건을 적고 열어 뒀다. 전부 고치는 것이 목표가 아니다.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>실패의 출처</t>
+          <t>테스트 스텝 확정</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>신규 7건 중 셋(UI-12 · UI-13 · BLD-10)이 수행 목록이 아니라 캡처와 로그에서 나왔다. 2회전에는 캡처 검토와 로그 확인을 세션 단계로 넣는다.</t>
+          <t>1차에 109칸이 비어 있던 스텝 열을 2차를 밟으며 채우고 확정했다. 제출물에 남아 있던 유일한 미확정 표시를 뗐다.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>TC 자체의 결함</t>
+          <t>판정 근거를 옮긴 셋</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>존재하지 않는 조작(EDGE-22) · 한 항목이 두 대상(EDGE-23) · 규칙이 다른 둘을 묶음(ENM-03). 수행은 제품만이 아니라 TC 도 검사한다.</t>
+          <t>시드 값 → 런 시작 줄 개수(TickCount 충돌), 인스펙터 → Player.log(열어 본 것만 보인다), 눈 → Loaded Objects. 틀린 판정은 안 나왔지만 운이지 절차의 성질이 아니었다.</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9055,7 +9055,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>EditMode 테스트 21개. Unity Test Runner 에서 실행하며 씬·플레이 모드가 필요 없다.</t>
+          <t>유니티 에디터 테스트(EditMode) 21개. Unity Test Runner 에서 실행하며 씬·플레이 모드가 필요 없다.</t>
         </is>
       </c>
     </row>
@@ -9063,6 +9063,13 @@
       <c r="A25" s="10" t="inlineStr">
         <is>
           <t>계산 검증은 SerializedObject 로 만든 픽스처를, 데이터 검증은 AssetDatabase 로 읽은 실제 에셋을 쓴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>[결과] 는 2차 수행(2026-10-04) 기준이다. Game.Gameplay.Tests 어셈블리 21개가 0.101초에 전부 통과했다.</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9134,7 +9141,7 @@
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
-          <t>첨부</t>
+          <t>처리</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9186,7 @@
       </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
-          <t>result_en.png · result.png</t>
+          <t>수정 · 확인</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9231,7 @@
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>reward.png</t>
+          <t>수정 · 확인</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9276,7 @@
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>boss.png</t>
+          <t>수정 · 확인</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9321,7 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>pause.png</t>
+          <t>수정 · 확인</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9366,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>controls.png · controls_en.png</t>
+          <t>수정 · 확인</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9411,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>reward.png</t>
+          <t>안 고침 — Trivial · 판단 기록</t>
         </is>
       </c>
     </row>
@@ -9449,7 +9456,149 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Player.log</t>
+          <t>수정 · 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>#165</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>설정 닫기 버튼으로 나가면 게임이 멈춘 채로 남는다</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>TC-UI-03</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>2차 세션 5</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>수정 · 빌드 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>#166</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>일시정지 중에 무기 교체가 된다</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>TC-EDGE-21</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>2차 세션 5</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>후속 — 입력 차단은 별건</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>#167</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>클리어 결과의 구분자가 플레이어에 가려진다</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>TC-UI-13</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>2차 세션 6</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Trivial</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>안 고침 — Trivial · 판단 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>수정 6 · 판단해서 안 고침 2 · 후속 2. 전부 고치는 것이 아니라 무엇을 안 고칠지 정하고 근거를 남기는 것도 결과다.</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9592,7 +9741,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>재현됨. 고치지 않은 근거가 기록에 있다 — 범위가 1차에 없다</t>
+          <t>2차에서도 재현됨. 범위가 1차에 없다 — 상세는 #143</t>
         </is>
       </c>
     </row>
@@ -9613,10 +9762,61 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>이연</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>TC-EDGE-21 일시정지 중 조작</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>#166 — 일시정지가 timeScale 만 멈추고 입력을 막지 않는다. 후속으로 둔다</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>못 한 것과 안 하기로 한 것은 다르다. 범위 밖은 정한 것이고, 미확인(△)은 0건이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>이연</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>#143 거절된 패턴이 쿨다운을 소모</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>2차 뒤 판단. 고치면 밸런스가 바뀌는데 확인할 차수가 없어 조건을 적고 열어 뒀다</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>안 고침</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>TC-UI-12 · #167 결과 화면 표시</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Trivial. 동작이 아니라 보기 문제라 근거를 적고 닫았다</t>
         </is>
       </c>
     </row>
